--- a/backend/src/utils/报名表.xlsx
+++ b/backend/src/utils/报名表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\document\dev\sportsmeet\backend\src\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5069" uniqueCount="1886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5068" uniqueCount="1886">
   <si>
     <t>年级</t>
   </si>
@@ -1141,21 +1141,21 @@
     <t>0185</t>
   </si>
   <si>
+    <t>汪梓煜</t>
+  </si>
+  <si>
+    <t>0186</t>
+  </si>
+  <si>
     <t>吴雨泽</t>
   </si>
   <si>
-    <t>0186</t>
+    <t>0187</t>
   </si>
   <si>
     <t>张威</t>
   </si>
   <si>
-    <t>0187</t>
-  </si>
-  <si>
-    <t>汪梓煜</t>
-  </si>
-  <si>
     <t>0191</t>
   </si>
   <si>
@@ -1669,15 +1669,15 @@
     <t>0305</t>
   </si>
   <si>
+    <t>胡俊</t>
+  </si>
+  <si>
+    <t>0306</t>
+  </si>
+  <si>
     <t>甘昊</t>
   </si>
   <si>
-    <t>0306</t>
-  </si>
-  <si>
-    <t>胡俊</t>
-  </si>
-  <si>
     <t>0311</t>
   </si>
   <si>
@@ -1693,25 +1693,25 @@
     <t>0313</t>
   </si>
   <si>
+    <t>熊文婷</t>
+  </si>
+  <si>
+    <t>0314</t>
+  </si>
+  <si>
+    <t>柴韵</t>
+  </si>
+  <si>
+    <t>0315</t>
+  </si>
+  <si>
     <t>刘永怡</t>
   </si>
   <si>
-    <t>0314</t>
+    <t>0316</t>
   </si>
   <si>
     <t>王紫嫣</t>
-  </si>
-  <si>
-    <t>0315</t>
-  </si>
-  <si>
-    <t>熊文婷</t>
-  </si>
-  <si>
-    <t>0316</t>
-  </si>
-  <si>
-    <t>柴韵</t>
   </si>
   <si>
     <t>0321</t>
@@ -5862,18 +5862,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -6194,7 +6188,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -6218,16 +6212,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -6236,89 +6230,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -6326,9 +6320,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
@@ -6645,8 +6636,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H943"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G943"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="9" style="2"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -6679,7 +6670,7 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C2">
@@ -6699,7 +6690,7 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C3">
@@ -6719,7 +6710,7 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C4">
@@ -6739,7 +6730,7 @@
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C5">
@@ -6759,7 +6750,7 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C6">
@@ -6782,7 +6773,7 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C7">
@@ -6802,7 +6793,7 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C8">
@@ -6822,7 +6813,7 @@
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C9">
@@ -6842,7 +6833,7 @@
       <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10">
@@ -6865,7 +6856,7 @@
       <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C11">
@@ -6885,7 +6876,7 @@
       <c r="A12" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C12">
@@ -6908,7 +6899,7 @@
       <c r="A13" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C13">
@@ -6931,7 +6922,7 @@
       <c r="A14" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C14">
@@ -6954,7 +6945,7 @@
       <c r="A15" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C15">
@@ -6974,7 +6965,7 @@
       <c r="A16" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C16">
@@ -6997,7 +6988,7 @@
       <c r="A17" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C17">
@@ -7020,7 +7011,7 @@
       <c r="A18" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C18">
@@ -7043,7 +7034,7 @@
       <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C19">
@@ -7066,7 +7057,7 @@
       <c r="A20" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C20">
@@ -7086,7 +7077,7 @@
       <c r="A21" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C21">
@@ -7109,7 +7100,7 @@
       <c r="A22" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C22">
@@ -7129,7 +7120,7 @@
       <c r="A23" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C23">
@@ -7149,7 +7140,7 @@
       <c r="A24" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C24">
@@ -7169,7 +7160,7 @@
       <c r="A25" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C25">
@@ -7189,7 +7180,7 @@
       <c r="A26" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C26">
@@ -7209,7 +7200,7 @@
       <c r="A27" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C27">
@@ -7229,7 +7220,7 @@
       <c r="A28" t="s">
         <v>7</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C28">
@@ -7249,7 +7240,7 @@
       <c r="A29" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C29">
@@ -7269,7 +7260,7 @@
       <c r="A30" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C30">
@@ -7292,7 +7283,7 @@
       <c r="A31" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C31">
@@ -7312,7 +7303,7 @@
       <c r="A32" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C32">
@@ -7335,7 +7326,7 @@
       <c r="A33" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C33">
@@ -7355,7 +7346,7 @@
       <c r="A34" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C34">
@@ -7375,7 +7366,7 @@
       <c r="A35" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C35">
@@ -7395,7 +7386,7 @@
       <c r="A36" t="s">
         <v>7</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C36">
@@ -7415,7 +7406,7 @@
       <c r="A37" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C37">
@@ -7438,7 +7429,7 @@
       <c r="A38" t="s">
         <v>7</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C38">
@@ -7458,7 +7449,7 @@
       <c r="A39" t="s">
         <v>7</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>92</v>
       </c>
       <c r="C39">
@@ -7481,7 +7472,7 @@
       <c r="A40" t="s">
         <v>7</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C40">
@@ -7504,7 +7495,7 @@
       <c r="A41" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C41">
@@ -7527,7 +7518,7 @@
       <c r="A42" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C42">
@@ -7550,7 +7541,7 @@
       <c r="A43" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C43">
@@ -7570,7 +7561,7 @@
       <c r="A44" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C44">
@@ -7590,7 +7581,7 @@
       <c r="A45" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C45">
@@ -7610,7 +7601,7 @@
       <c r="A46" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>106</v>
       </c>
       <c r="C46">
@@ -7630,7 +7621,7 @@
       <c r="A47" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C47">
@@ -7650,7 +7641,7 @@
       <c r="A48" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C48">
@@ -7670,7 +7661,7 @@
       <c r="A49" t="s">
         <v>7</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C49">
@@ -7690,7 +7681,7 @@
       <c r="A50" t="s">
         <v>7</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>114</v>
       </c>
       <c r="C50">
@@ -7710,7 +7701,7 @@
       <c r="A51" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C51">
@@ -7730,7 +7721,7 @@
       <c r="A52" t="s">
         <v>7</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C52">
@@ -7750,7 +7741,7 @@
       <c r="A53" t="s">
         <v>7</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C53">
@@ -7770,7 +7761,7 @@
       <c r="A54" t="s">
         <v>7</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>122</v>
       </c>
       <c r="C54">
@@ -7790,7 +7781,7 @@
       <c r="A55" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="3" t="s">
         <v>124</v>
       </c>
       <c r="C55">
@@ -7810,7 +7801,7 @@
       <c r="A56" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C56">
@@ -7830,7 +7821,7 @@
       <c r="A57" t="s">
         <v>7</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>128</v>
       </c>
       <c r="C57">
@@ -7850,7 +7841,7 @@
       <c r="A58" t="s">
         <v>7</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C58">
@@ -7870,7 +7861,7 @@
       <c r="A59" t="s">
         <v>7</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="3" t="s">
         <v>132</v>
       </c>
       <c r="C59">
@@ -7890,7 +7881,7 @@
       <c r="A60" t="s">
         <v>7</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="3" t="s">
         <v>134</v>
       </c>
       <c r="C60">
@@ -7910,7 +7901,7 @@
       <c r="A61" t="s">
         <v>7</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="3" t="s">
         <v>136</v>
       </c>
       <c r="C61">
@@ -7930,7 +7921,7 @@
       <c r="A62" t="s">
         <v>7</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="3" t="s">
         <v>138</v>
       </c>
       <c r="C62">
@@ -7950,7 +7941,7 @@
       <c r="A63" t="s">
         <v>7</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C63">
@@ -7970,7 +7961,7 @@
       <c r="A64" t="s">
         <v>7</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>142</v>
       </c>
       <c r="C64">
@@ -7990,7 +7981,7 @@
       <c r="A65" t="s">
         <v>7</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="3" t="s">
         <v>144</v>
       </c>
       <c r="C65">
@@ -8010,7 +8001,7 @@
       <c r="A66" t="s">
         <v>7</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="3" t="s">
         <v>146</v>
       </c>
       <c r="C66">
@@ -8030,7 +8021,7 @@
       <c r="A67" t="s">
         <v>7</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="3" t="s">
         <v>148</v>
       </c>
       <c r="C67">
@@ -8050,7 +8041,7 @@
       <c r="A68" t="s">
         <v>7</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C68">
@@ -8070,7 +8061,7 @@
       <c r="A69" t="s">
         <v>7</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C69">
@@ -8090,7 +8081,7 @@
       <c r="A70" t="s">
         <v>7</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="3" t="s">
         <v>154</v>
       </c>
       <c r="C70">
@@ -8113,7 +8104,7 @@
       <c r="A71" t="s">
         <v>7</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="3" t="s">
         <v>156</v>
       </c>
       <c r="C71">
@@ -8136,7 +8127,7 @@
       <c r="A72" t="s">
         <v>7</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="3" t="s">
         <v>158</v>
       </c>
       <c r="C72">
@@ -8156,7 +8147,7 @@
       <c r="A73" t="s">
         <v>7</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C73">
@@ -8176,7 +8167,7 @@
       <c r="A74" t="s">
         <v>7</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="3" t="s">
         <v>162</v>
       </c>
       <c r="C74">
@@ -8196,7 +8187,7 @@
       <c r="A75" t="s">
         <v>7</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C75">
@@ -8216,7 +8207,7 @@
       <c r="A76" t="s">
         <v>7</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="3" t="s">
         <v>166</v>
       </c>
       <c r="C76">
@@ -8236,7 +8227,7 @@
       <c r="A77" t="s">
         <v>7</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C77">
@@ -8256,7 +8247,7 @@
       <c r="A78" t="s">
         <v>7</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="3" t="s">
         <v>170</v>
       </c>
       <c r="C78">
@@ -8279,7 +8270,7 @@
       <c r="A79" t="s">
         <v>7</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="3" t="s">
         <v>172</v>
       </c>
       <c r="C79">
@@ -8302,7 +8293,7 @@
       <c r="A80" t="s">
         <v>7</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="3" t="s">
         <v>174</v>
       </c>
       <c r="C80">
@@ -8322,7 +8313,7 @@
       <c r="A81" t="s">
         <v>7</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="3" t="s">
         <v>176</v>
       </c>
       <c r="C81">
@@ -8342,7 +8333,7 @@
       <c r="A82" t="s">
         <v>7</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="3" t="s">
         <v>178</v>
       </c>
       <c r="C82">
@@ -8365,7 +8356,7 @@
       <c r="A83" t="s">
         <v>7</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="3" t="s">
         <v>180</v>
       </c>
       <c r="C83">
@@ -8388,7 +8379,7 @@
       <c r="A84" t="s">
         <v>7</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="3" t="s">
         <v>182</v>
       </c>
       <c r="C84">
@@ -8408,7 +8399,7 @@
       <c r="A85" t="s">
         <v>7</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="3" t="s">
         <v>184</v>
       </c>
       <c r="C85">
@@ -8428,7 +8419,7 @@
       <c r="A86" t="s">
         <v>7</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="3" t="s">
         <v>186</v>
       </c>
       <c r="C86">
@@ -8448,7 +8439,7 @@
       <c r="A87" t="s">
         <v>7</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C87">
@@ -8468,7 +8459,7 @@
       <c r="A88" t="s">
         <v>7</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="3" t="s">
         <v>190</v>
       </c>
       <c r="C88">
@@ -8488,7 +8479,7 @@
       <c r="A89" t="s">
         <v>7</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C89">
@@ -8511,7 +8502,7 @@
       <c r="A90" t="s">
         <v>7</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C90">
@@ -8534,7 +8525,7 @@
       <c r="A91" t="s">
         <v>7</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C91">
@@ -8554,7 +8545,7 @@
       <c r="A92" t="s">
         <v>7</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C92">
@@ -8574,7 +8565,7 @@
       <c r="A93" t="s">
         <v>7</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C93">
@@ -8594,7 +8585,7 @@
       <c r="A94" t="s">
         <v>7</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C94">
@@ -8617,7 +8608,7 @@
       <c r="A95" t="s">
         <v>7</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="3" t="s">
         <v>204</v>
       </c>
       <c r="C95">
@@ -8637,7 +8628,7 @@
       <c r="A96" t="s">
         <v>7</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="3" t="s">
         <v>206</v>
       </c>
       <c r="C96">
@@ -8660,7 +8651,7 @@
       <c r="A97" t="s">
         <v>7</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C97">
@@ -8683,7 +8674,7 @@
       <c r="A98" t="s">
         <v>7</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="3" t="s">
         <v>210</v>
       </c>
       <c r="C98">
@@ -8706,7 +8697,7 @@
       <c r="A99" t="s">
         <v>7</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="3" t="s">
         <v>212</v>
       </c>
       <c r="C99">
@@ -8726,7 +8717,7 @@
       <c r="A100" t="s">
         <v>7</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C100">
@@ -8746,7 +8737,7 @@
       <c r="A101" t="s">
         <v>7</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C101">
@@ -8766,7 +8757,7 @@
       <c r="A102" t="s">
         <v>7</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="3" t="s">
         <v>218</v>
       </c>
       <c r="C102">
@@ -8786,7 +8777,7 @@
       <c r="A103" t="s">
         <v>7</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="3" t="s">
         <v>220</v>
       </c>
       <c r="C103">
@@ -8809,7 +8800,7 @@
       <c r="A104" t="s">
         <v>7</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C104">
@@ -8832,7 +8823,7 @@
       <c r="A105" t="s">
         <v>7</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="3" t="s">
         <v>224</v>
       </c>
       <c r="C105">
@@ -8852,7 +8843,7 @@
       <c r="A106" t="s">
         <v>7</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="3" t="s">
         <v>226</v>
       </c>
       <c r="C106">
@@ -8875,7 +8866,7 @@
       <c r="A107" t="s">
         <v>7</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="3" t="s">
         <v>228</v>
       </c>
       <c r="C107">
@@ -8898,7 +8889,7 @@
       <c r="A108" t="s">
         <v>7</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="3" t="s">
         <v>230</v>
       </c>
       <c r="C108">
@@ -8918,7 +8909,7 @@
       <c r="A109" t="s">
         <v>7</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="3" t="s">
         <v>232</v>
       </c>
       <c r="C109">
@@ -8941,7 +8932,7 @@
       <c r="A110" t="s">
         <v>7</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C110">
@@ -8964,7 +8955,7 @@
       <c r="A111" t="s">
         <v>7</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="3" t="s">
         <v>236</v>
       </c>
       <c r="C111">
@@ -8987,7 +8978,7 @@
       <c r="A112" t="s">
         <v>7</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C112">
@@ -9007,7 +8998,7 @@
       <c r="A113" t="s">
         <v>7</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="3" t="s">
         <v>240</v>
       </c>
       <c r="C113">
@@ -9030,7 +9021,7 @@
       <c r="A114" t="s">
         <v>7</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="3" t="s">
         <v>242</v>
       </c>
       <c r="C114">
@@ -9050,7 +9041,7 @@
       <c r="A115" t="s">
         <v>7</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="3" t="s">
         <v>244</v>
       </c>
       <c r="C115">
@@ -9070,7 +9061,7 @@
       <c r="A116" t="s">
         <v>7</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="3" t="s">
         <v>246</v>
       </c>
       <c r="C116">
@@ -9093,7 +9084,7 @@
       <c r="A117" t="s">
         <v>7</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="3" t="s">
         <v>248</v>
       </c>
       <c r="C117">
@@ -9108,15 +9099,12 @@
       <c r="F117" t="s">
         <v>17</v>
       </c>
-      <c r="G117" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>7</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="3" t="s">
         <v>250</v>
       </c>
       <c r="C118">
@@ -9136,7 +9124,7 @@
       <c r="A119" t="s">
         <v>7</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="3" t="s">
         <v>252</v>
       </c>
       <c r="C119">
@@ -9156,7 +9144,7 @@
       <c r="A120" t="s">
         <v>7</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="3" t="s">
         <v>254</v>
       </c>
       <c r="C120">
@@ -9179,7 +9167,7 @@
       <c r="A121" t="s">
         <v>7</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="3" t="s">
         <v>256</v>
       </c>
       <c r="C121">
@@ -9199,7 +9187,7 @@
       <c r="A122" t="s">
         <v>7</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="3" t="s">
         <v>258</v>
       </c>
       <c r="C122">
@@ -9219,7 +9207,7 @@
       <c r="A123" t="s">
         <v>7</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="3" t="s">
         <v>260</v>
       </c>
       <c r="C123">
@@ -9239,7 +9227,7 @@
       <c r="A124" t="s">
         <v>7</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="3" t="s">
         <v>262</v>
       </c>
       <c r="C124">
@@ -9259,7 +9247,7 @@
       <c r="A125" t="s">
         <v>7</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="3" t="s">
         <v>264</v>
       </c>
       <c r="C125">
@@ -9279,7 +9267,7 @@
       <c r="A126" t="s">
         <v>7</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="3" t="s">
         <v>266</v>
       </c>
       <c r="C126">
@@ -9302,7 +9290,7 @@
       <c r="A127" t="s">
         <v>7</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="3" t="s">
         <v>268</v>
       </c>
       <c r="C127">
@@ -9322,7 +9310,7 @@
       <c r="A128" t="s">
         <v>7</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="3" t="s">
         <v>270</v>
       </c>
       <c r="C128">
@@ -9342,7 +9330,7 @@
       <c r="A129" t="s">
         <v>7</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="3" t="s">
         <v>272</v>
       </c>
       <c r="C129">
@@ -9362,7 +9350,7 @@
       <c r="A130" t="s">
         <v>7</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="3" t="s">
         <v>274</v>
       </c>
       <c r="C130">
@@ -9382,7 +9370,7 @@
       <c r="A131" t="s">
         <v>7</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="3" t="s">
         <v>276</v>
       </c>
       <c r="C131">
@@ -9402,7 +9390,7 @@
       <c r="A132" t="s">
         <v>7</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="3" t="s">
         <v>278</v>
       </c>
       <c r="C132">
@@ -9425,7 +9413,7 @@
       <c r="A133" t="s">
         <v>7</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="3" t="s">
         <v>280</v>
       </c>
       <c r="C133">
@@ -9448,7 +9436,7 @@
       <c r="A134" t="s">
         <v>7</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="3" t="s">
         <v>282</v>
       </c>
       <c r="C134">
@@ -9471,7 +9459,7 @@
       <c r="A135" t="s">
         <v>7</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C135">
@@ -9494,7 +9482,7 @@
       <c r="A136" t="s">
         <v>7</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="3" t="s">
         <v>286</v>
       </c>
       <c r="C136">
@@ -9517,7 +9505,7 @@
       <c r="A137" t="s">
         <v>7</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="3" t="s">
         <v>288</v>
       </c>
       <c r="C137">
@@ -9540,7 +9528,7 @@
       <c r="A138" t="s">
         <v>7</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="3" t="s">
         <v>290</v>
       </c>
       <c r="C138">
@@ -9563,7 +9551,7 @@
       <c r="A139" t="s">
         <v>7</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" s="3" t="s">
         <v>292</v>
       </c>
       <c r="C139">
@@ -9586,7 +9574,7 @@
       <c r="A140" t="s">
         <v>7</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="3" t="s">
         <v>294</v>
       </c>
       <c r="C140">
@@ -9609,7 +9597,7 @@
       <c r="A141" t="s">
         <v>7</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="3" t="s">
         <v>296</v>
       </c>
       <c r="C141">
@@ -9632,7 +9620,7 @@
       <c r="A142" t="s">
         <v>7</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="3" t="s">
         <v>298</v>
       </c>
       <c r="C142">
@@ -9655,7 +9643,7 @@
       <c r="A143" t="s">
         <v>7</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" s="3" t="s">
         <v>300</v>
       </c>
       <c r="C143">
@@ -9678,7 +9666,7 @@
       <c r="A144" t="s">
         <v>7</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="3" t="s">
         <v>302</v>
       </c>
       <c r="C144">
@@ -9701,7 +9689,7 @@
       <c r="A145" t="s">
         <v>7</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="3" t="s">
         <v>304</v>
       </c>
       <c r="C145">
@@ -9724,7 +9712,7 @@
       <c r="A146" t="s">
         <v>7</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="3" t="s">
         <v>306</v>
       </c>
       <c r="C146">
@@ -9747,7 +9735,7 @@
       <c r="A147" t="s">
         <v>7</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B147" s="3" t="s">
         <v>308</v>
       </c>
       <c r="C147">
@@ -9770,7 +9758,7 @@
       <c r="A148" t="s">
         <v>7</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B148" s="3" t="s">
         <v>310</v>
       </c>
       <c r="C148">
@@ -9793,7 +9781,7 @@
       <c r="A149" t="s">
         <v>7</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" s="3" t="s">
         <v>312</v>
       </c>
       <c r="C149">
@@ -9816,7 +9804,7 @@
       <c r="A150" t="s">
         <v>7</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="3" t="s">
         <v>314</v>
       </c>
       <c r="C150">
@@ -9839,7 +9827,7 @@
       <c r="A151" t="s">
         <v>7</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="3" t="s">
         <v>316</v>
       </c>
       <c r="C151">
@@ -9862,7 +9850,7 @@
       <c r="A152" t="s">
         <v>7</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="3" t="s">
         <v>318</v>
       </c>
       <c r="C152">
@@ -9885,7 +9873,7 @@
       <c r="A153" t="s">
         <v>7</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B153" s="3" t="s">
         <v>320</v>
       </c>
       <c r="C153">
@@ -9908,7 +9896,7 @@
       <c r="A154" t="s">
         <v>7</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B154" s="3" t="s">
         <v>322</v>
       </c>
       <c r="C154">
@@ -9928,7 +9916,7 @@
       <c r="A155" t="s">
         <v>7</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="3" t="s">
         <v>324</v>
       </c>
       <c r="C155">
@@ -9948,7 +9936,7 @@
       <c r="A156" t="s">
         <v>7</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B156" s="3" t="s">
         <v>326</v>
       </c>
       <c r="C156">
@@ -9971,7 +9959,7 @@
       <c r="A157" t="s">
         <v>7</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" s="3" t="s">
         <v>328</v>
       </c>
       <c r="C157">
@@ -9991,7 +9979,7 @@
       <c r="A158" t="s">
         <v>7</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="3" t="s">
         <v>330</v>
       </c>
       <c r="C158">
@@ -10014,7 +10002,7 @@
       <c r="A159" t="s">
         <v>7</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" s="3" t="s">
         <v>332</v>
       </c>
       <c r="C159">
@@ -10034,7 +10022,7 @@
       <c r="A160" t="s">
         <v>7</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="3" t="s">
         <v>334</v>
       </c>
       <c r="C160">
@@ -10057,7 +10045,7 @@
       <c r="A161" t="s">
         <v>7</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="3" t="s">
         <v>336</v>
       </c>
       <c r="C161">
@@ -10080,7 +10068,7 @@
       <c r="A162" t="s">
         <v>7</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" s="3" t="s">
         <v>338</v>
       </c>
       <c r="C162">
@@ -10100,7 +10088,7 @@
       <c r="A163" t="s">
         <v>7</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B163" s="3" t="s">
         <v>340</v>
       </c>
       <c r="C163">
@@ -10123,7 +10111,7 @@
       <c r="A164" t="s">
         <v>7</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B164" s="3" t="s">
         <v>342</v>
       </c>
       <c r="C164">
@@ -10143,7 +10131,7 @@
       <c r="A165" t="s">
         <v>7</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="3" t="s">
         <v>344</v>
       </c>
       <c r="C165">
@@ -10163,7 +10151,7 @@
       <c r="A166" t="s">
         <v>7</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="3" t="s">
         <v>346</v>
       </c>
       <c r="C166">
@@ -10183,7 +10171,7 @@
       <c r="A167" t="s">
         <v>7</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" s="3" t="s">
         <v>348</v>
       </c>
       <c r="C167">
@@ -10203,7 +10191,7 @@
       <c r="A168" t="s">
         <v>7</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" s="3" t="s">
         <v>350</v>
       </c>
       <c r="C168">
@@ -10223,7 +10211,7 @@
       <c r="A169" t="s">
         <v>7</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="3" t="s">
         <v>352</v>
       </c>
       <c r="C169">
@@ -10243,7 +10231,7 @@
       <c r="A170" t="s">
         <v>7</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" s="3" t="s">
         <v>354</v>
       </c>
       <c r="C170">
@@ -10263,7 +10251,7 @@
       <c r="A171" t="s">
         <v>7</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B171" s="3" t="s">
         <v>356</v>
       </c>
       <c r="C171">
@@ -10283,7 +10271,7 @@
       <c r="A172" t="s">
         <v>7</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B172" s="3" t="s">
         <v>358</v>
       </c>
       <c r="C172">
@@ -10306,7 +10294,7 @@
       <c r="A173" t="s">
         <v>7</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" s="3" t="s">
         <v>360</v>
       </c>
       <c r="C173">
@@ -10329,7 +10317,7 @@
       <c r="A174" t="s">
         <v>7</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="B174" s="3" t="s">
         <v>362</v>
       </c>
       <c r="C174">
@@ -10352,7 +10340,7 @@
       <c r="A175" t="s">
         <v>7</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B175" s="3" t="s">
         <v>364</v>
       </c>
       <c r="C175">
@@ -10372,7 +10360,7 @@
       <c r="A176" t="s">
         <v>7</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="3" t="s">
         <v>366</v>
       </c>
       <c r="C176">
@@ -10385,14 +10373,17 @@
         <v>367</v>
       </c>
       <c r="F176" t="s">
-        <v>14</v>
+        <v>64</v>
+      </c>
+      <c r="G176" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
         <v>7</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B177" s="3" t="s">
         <v>368</v>
       </c>
       <c r="C177">
@@ -10405,17 +10396,14 @@
         <v>369</v>
       </c>
       <c r="F177" t="s">
-        <v>64</v>
-      </c>
-      <c r="G177" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
         <v>7</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="B178" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C178">
@@ -10438,7 +10426,7 @@
       <c r="A179" t="s">
         <v>7</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="3" t="s">
         <v>372</v>
       </c>
       <c r="C179">
@@ -10461,7 +10449,7 @@
       <c r="A180" t="s">
         <v>7</v>
       </c>
-      <c r="B180" s="4" t="s">
+      <c r="B180" s="3" t="s">
         <v>374</v>
       </c>
       <c r="C180">
@@ -10484,7 +10472,7 @@
       <c r="A181" t="s">
         <v>7</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B181" s="3" t="s">
         <v>376</v>
       </c>
       <c r="C181">
@@ -10504,7 +10492,7 @@
       <c r="A182" t="s">
         <v>7</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B182" s="3" t="s">
         <v>378</v>
       </c>
       <c r="C182">
@@ -10524,7 +10512,7 @@
       <c r="A183" t="s">
         <v>7</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B183" s="3" t="s">
         <v>380</v>
       </c>
       <c r="C183">
@@ -10544,7 +10532,7 @@
       <c r="A184" t="s">
         <v>7</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="B184" s="3" t="s">
         <v>382</v>
       </c>
       <c r="C184">
@@ -10567,7 +10555,7 @@
       <c r="A185" t="s">
         <v>7</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B185" s="3" t="s">
         <v>384</v>
       </c>
       <c r="C185">
@@ -10587,7 +10575,7 @@
       <c r="A186" t="s">
         <v>7</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="B186" s="3" t="s">
         <v>386</v>
       </c>
       <c r="C186">
@@ -10607,7 +10595,7 @@
       <c r="A187" t="s">
         <v>7</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="B187" s="3" t="s">
         <v>388</v>
       </c>
       <c r="C187">
@@ -10627,7 +10615,7 @@
       <c r="A188" t="s">
         <v>7</v>
       </c>
-      <c r="B188" s="4" t="s">
+      <c r="B188" s="3" t="s">
         <v>390</v>
       </c>
       <c r="C188">
@@ -10650,7 +10638,7 @@
       <c r="A189" t="s">
         <v>7</v>
       </c>
-      <c r="B189" s="4" t="s">
+      <c r="B189" s="3" t="s">
         <v>392</v>
       </c>
       <c r="C189">
@@ -10670,7 +10658,7 @@
       <c r="A190" t="s">
         <v>7</v>
       </c>
-      <c r="B190" s="4" t="s">
+      <c r="B190" s="3" t="s">
         <v>394</v>
       </c>
       <c r="C190">
@@ -10690,7 +10678,7 @@
       <c r="A191" t="s">
         <v>7</v>
       </c>
-      <c r="B191" s="4" t="s">
+      <c r="B191" s="3" t="s">
         <v>396</v>
       </c>
       <c r="C191">
@@ -10710,7 +10698,7 @@
       <c r="A192" t="s">
         <v>7</v>
       </c>
-      <c r="B192" s="4" t="s">
+      <c r="B192" s="3" t="s">
         <v>398</v>
       </c>
       <c r="C192">
@@ -10730,7 +10718,7 @@
       <c r="A193" t="s">
         <v>7</v>
       </c>
-      <c r="B193" s="4" t="s">
+      <c r="B193" s="3" t="s">
         <v>400</v>
       </c>
       <c r="C193">
@@ -10750,7 +10738,7 @@
       <c r="A194" t="s">
         <v>7</v>
       </c>
-      <c r="B194" s="4" t="s">
+      <c r="B194" s="3" t="s">
         <v>402</v>
       </c>
       <c r="C194">
@@ -10773,7 +10761,7 @@
       <c r="A195" t="s">
         <v>7</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B195" s="3" t="s">
         <v>404</v>
       </c>
       <c r="C195">
@@ -10793,7 +10781,7 @@
       <c r="A196" t="s">
         <v>7</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" s="3" t="s">
         <v>406</v>
       </c>
       <c r="C196">
@@ -10816,7 +10804,7 @@
       <c r="A197" t="s">
         <v>7</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B197" s="3" t="s">
         <v>408</v>
       </c>
       <c r="C197">
@@ -10839,7 +10827,7 @@
       <c r="A198" t="s">
         <v>7</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B198" s="3" t="s">
         <v>410</v>
       </c>
       <c r="C198">
@@ -10859,7 +10847,7 @@
       <c r="A199" t="s">
         <v>7</v>
       </c>
-      <c r="B199" s="4" t="s">
+      <c r="B199" s="3" t="s">
         <v>412</v>
       </c>
       <c r="C199">
@@ -10879,7 +10867,7 @@
       <c r="A200" t="s">
         <v>7</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B200" s="3" t="s">
         <v>414</v>
       </c>
       <c r="C200">
@@ -10902,7 +10890,7 @@
       <c r="A201" t="s">
         <v>7</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B201" s="3" t="s">
         <v>416</v>
       </c>
       <c r="C201">
@@ -10925,7 +10913,7 @@
       <c r="A202" t="s">
         <v>7</v>
       </c>
-      <c r="B202" s="4" t="s">
+      <c r="B202" s="3" t="s">
         <v>418</v>
       </c>
       <c r="C202">
@@ -10945,7 +10933,7 @@
       <c r="A203" t="s">
         <v>7</v>
       </c>
-      <c r="B203" s="4" t="s">
+      <c r="B203" s="3" t="s">
         <v>420</v>
       </c>
       <c r="C203">
@@ -10968,7 +10956,7 @@
       <c r="A204" t="s">
         <v>7</v>
       </c>
-      <c r="B204" s="4" t="s">
+      <c r="B204" s="3" t="s">
         <v>422</v>
       </c>
       <c r="C204">
@@ -10988,7 +10976,7 @@
       <c r="A205" t="s">
         <v>7</v>
       </c>
-      <c r="B205" s="4" t="s">
+      <c r="B205" s="3" t="s">
         <v>424</v>
       </c>
       <c r="C205">
@@ -11008,7 +10996,7 @@
       <c r="A206" t="s">
         <v>7</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" s="3" t="s">
         <v>426</v>
       </c>
       <c r="C206">
@@ -11028,7 +11016,7 @@
       <c r="A207" t="s">
         <v>7</v>
       </c>
-      <c r="B207" s="4" t="s">
+      <c r="B207" s="3" t="s">
         <v>428</v>
       </c>
       <c r="C207">
@@ -11048,7 +11036,7 @@
       <c r="A208" t="s">
         <v>7</v>
       </c>
-      <c r="B208" s="4" t="s">
+      <c r="B208" s="3" t="s">
         <v>430</v>
       </c>
       <c r="C208">
@@ -11068,7 +11056,7 @@
       <c r="A209" t="s">
         <v>7</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B209" s="3" t="s">
         <v>432</v>
       </c>
       <c r="C209">
@@ -11088,7 +11076,7 @@
       <c r="A210" t="s">
         <v>7</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="B210" s="3" t="s">
         <v>434</v>
       </c>
       <c r="C210">
@@ -11108,7 +11096,7 @@
       <c r="A211" t="s">
         <v>7</v>
       </c>
-      <c r="B211" s="4" t="s">
+      <c r="B211" s="3" t="s">
         <v>436</v>
       </c>
       <c r="C211">
@@ -11128,7 +11116,7 @@
       <c r="A212" t="s">
         <v>7</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B212" s="3" t="s">
         <v>438</v>
       </c>
       <c r="C212">
@@ -11148,7 +11136,7 @@
       <c r="A213" t="s">
         <v>7</v>
       </c>
-      <c r="B213" s="4" t="s">
+      <c r="B213" s="3" t="s">
         <v>440</v>
       </c>
       <c r="C213">
@@ -11168,7 +11156,7 @@
       <c r="A214" t="s">
         <v>7</v>
       </c>
-      <c r="B214" s="4" t="s">
+      <c r="B214" s="3" t="s">
         <v>442</v>
       </c>
       <c r="C214">
@@ -11188,7 +11176,7 @@
       <c r="A215" t="s">
         <v>7</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="B215" s="3" t="s">
         <v>444</v>
       </c>
       <c r="C215">
@@ -11208,7 +11196,7 @@
       <c r="A216" t="s">
         <v>7</v>
       </c>
-      <c r="B216" s="4" t="s">
+      <c r="B216" s="3" t="s">
         <v>446</v>
       </c>
       <c r="C216">
@@ -11228,7 +11216,7 @@
       <c r="A217" t="s">
         <v>7</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B217" s="3" t="s">
         <v>448</v>
       </c>
       <c r="C217">
@@ -11248,7 +11236,7 @@
       <c r="A218" t="s">
         <v>7</v>
       </c>
-      <c r="B218" s="4" t="s">
+      <c r="B218" s="3" t="s">
         <v>450</v>
       </c>
       <c r="C218">
@@ -11268,7 +11256,7 @@
       <c r="A219" t="s">
         <v>7</v>
       </c>
-      <c r="B219" s="4" t="s">
+      <c r="B219" s="3" t="s">
         <v>452</v>
       </c>
       <c r="C219">
@@ -11291,7 +11279,7 @@
       <c r="A220" t="s">
         <v>7</v>
       </c>
-      <c r="B220" s="4" t="s">
+      <c r="B220" s="3" t="s">
         <v>454</v>
       </c>
       <c r="C220">
@@ -11311,7 +11299,7 @@
       <c r="A221" t="s">
         <v>7</v>
       </c>
-      <c r="B221" s="4" t="s">
+      <c r="B221" s="3" t="s">
         <v>456</v>
       </c>
       <c r="C221">
@@ -11331,7 +11319,7 @@
       <c r="A222" t="s">
         <v>7</v>
       </c>
-      <c r="B222" s="4" t="s">
+      <c r="B222" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C222">
@@ -11351,7 +11339,7 @@
       <c r="A223" t="s">
         <v>7</v>
       </c>
-      <c r="B223" s="4" t="s">
+      <c r="B223" s="3" t="s">
         <v>460</v>
       </c>
       <c r="C223">
@@ -11371,7 +11359,7 @@
       <c r="A224" t="s">
         <v>7</v>
       </c>
-      <c r="B224" s="4" t="s">
+      <c r="B224" s="3" t="s">
         <v>462</v>
       </c>
       <c r="C224">
@@ -11391,7 +11379,7 @@
       <c r="A225" t="s">
         <v>7</v>
       </c>
-      <c r="B225" s="4" t="s">
+      <c r="B225" s="3" t="s">
         <v>464</v>
       </c>
       <c r="C225">
@@ -11411,7 +11399,7 @@
       <c r="A226" t="s">
         <v>7</v>
       </c>
-      <c r="B226" s="4" t="s">
+      <c r="B226" s="3" t="s">
         <v>466</v>
       </c>
       <c r="C226">
@@ -11431,7 +11419,7 @@
       <c r="A227" t="s">
         <v>7</v>
       </c>
-      <c r="B227" s="4" t="s">
+      <c r="B227" s="3" t="s">
         <v>468</v>
       </c>
       <c r="C227">
@@ -11451,7 +11439,7 @@
       <c r="A228" t="s">
         <v>7</v>
       </c>
-      <c r="B228" s="4" t="s">
+      <c r="B228" s="3" t="s">
         <v>470</v>
       </c>
       <c r="C228">
@@ -11471,7 +11459,7 @@
       <c r="A229" t="s">
         <v>7</v>
       </c>
-      <c r="B229" s="4" t="s">
+      <c r="B229" s="3" t="s">
         <v>472</v>
       </c>
       <c r="C229">
@@ -11491,7 +11479,7 @@
       <c r="A230" t="s">
         <v>7</v>
       </c>
-      <c r="B230" s="4" t="s">
+      <c r="B230" s="3" t="s">
         <v>474</v>
       </c>
       <c r="C230">
@@ -11511,7 +11499,7 @@
       <c r="A231" t="s">
         <v>7</v>
       </c>
-      <c r="B231" s="4" t="s">
+      <c r="B231" s="3" t="s">
         <v>476</v>
       </c>
       <c r="C231">
@@ -11531,7 +11519,7 @@
       <c r="A232" t="s">
         <v>7</v>
       </c>
-      <c r="B232" s="4" t="s">
+      <c r="B232" s="3" t="s">
         <v>478</v>
       </c>
       <c r="C232">
@@ -11554,7 +11542,7 @@
       <c r="A233" t="s">
         <v>7</v>
       </c>
-      <c r="B233" s="4" t="s">
+      <c r="B233" s="3" t="s">
         <v>480</v>
       </c>
       <c r="C233">
@@ -11574,7 +11562,7 @@
       <c r="A234" t="s">
         <v>7</v>
       </c>
-      <c r="B234" s="4" t="s">
+      <c r="B234" s="3" t="s">
         <v>482</v>
       </c>
       <c r="C234">
@@ -11594,7 +11582,7 @@
       <c r="A235" t="s">
         <v>7</v>
       </c>
-      <c r="B235" s="4" t="s">
+      <c r="B235" s="3" t="s">
         <v>484</v>
       </c>
       <c r="C235">
@@ -11614,7 +11602,7 @@
       <c r="A236" t="s">
         <v>7</v>
       </c>
-      <c r="B236" s="4" t="s">
+      <c r="B236" s="3" t="s">
         <v>486</v>
       </c>
       <c r="C236">
@@ -11634,7 +11622,7 @@
       <c r="A237" t="s">
         <v>7</v>
       </c>
-      <c r="B237" s="4" t="s">
+      <c r="B237" s="3" t="s">
         <v>488</v>
       </c>
       <c r="C237">
@@ -11654,7 +11642,7 @@
       <c r="A238" t="s">
         <v>7</v>
       </c>
-      <c r="B238" s="4" t="s">
+      <c r="B238" s="3" t="s">
         <v>490</v>
       </c>
       <c r="C238">
@@ -11674,7 +11662,7 @@
       <c r="A239" t="s">
         <v>7</v>
       </c>
-      <c r="B239" s="4" t="s">
+      <c r="B239" s="3" t="s">
         <v>492</v>
       </c>
       <c r="C239">
@@ -11694,7 +11682,7 @@
       <c r="A240" t="s">
         <v>7</v>
       </c>
-      <c r="B240" s="4" t="s">
+      <c r="B240" s="3" t="s">
         <v>494</v>
       </c>
       <c r="C240">
@@ -11714,7 +11702,7 @@
       <c r="A241" t="s">
         <v>7</v>
       </c>
-      <c r="B241" s="4" t="s">
+      <c r="B241" s="3" t="s">
         <v>496</v>
       </c>
       <c r="C241">
@@ -11734,7 +11722,7 @@
       <c r="A242" t="s">
         <v>7</v>
       </c>
-      <c r="B242" s="4" t="s">
+      <c r="B242" s="3" t="s">
         <v>498</v>
       </c>
       <c r="C242">
@@ -11754,7 +11742,7 @@
       <c r="A243" t="s">
         <v>7</v>
       </c>
-      <c r="B243" s="4" t="s">
+      <c r="B243" s="3" t="s">
         <v>500</v>
       </c>
       <c r="C243">
@@ -11774,7 +11762,7 @@
       <c r="A244" t="s">
         <v>7</v>
       </c>
-      <c r="B244" s="4" t="s">
+      <c r="B244" s="3" t="s">
         <v>502</v>
       </c>
       <c r="C244">
@@ -11794,7 +11782,7 @@
       <c r="A245" t="s">
         <v>7</v>
       </c>
-      <c r="B245" s="4" t="s">
+      <c r="B245" s="3" t="s">
         <v>504</v>
       </c>
       <c r="C245">
@@ -11814,7 +11802,7 @@
       <c r="A246" t="s">
         <v>7</v>
       </c>
-      <c r="B246" s="4" t="s">
+      <c r="B246" s="3" t="s">
         <v>506</v>
       </c>
       <c r="C246">
@@ -11837,7 +11825,7 @@
       <c r="A247" t="s">
         <v>7</v>
       </c>
-      <c r="B247" s="4" t="s">
+      <c r="B247" s="3" t="s">
         <v>508</v>
       </c>
       <c r="C247">
@@ -11860,7 +11848,7 @@
       <c r="A248" t="s">
         <v>7</v>
       </c>
-      <c r="B248" s="4" t="s">
+      <c r="B248" s="3" t="s">
         <v>510</v>
       </c>
       <c r="C248">
@@ -11883,7 +11871,7 @@
       <c r="A249" t="s">
         <v>7</v>
       </c>
-      <c r="B249" s="4" t="s">
+      <c r="B249" s="3" t="s">
         <v>512</v>
       </c>
       <c r="C249">
@@ -11903,7 +11891,7 @@
       <c r="A250" t="s">
         <v>7</v>
       </c>
-      <c r="B250" s="4" t="s">
+      <c r="B250" s="3" t="s">
         <v>514</v>
       </c>
       <c r="C250">
@@ -11926,7 +11914,7 @@
       <c r="A251" t="s">
         <v>7</v>
       </c>
-      <c r="B251" s="4" t="s">
+      <c r="B251" s="3" t="s">
         <v>516</v>
       </c>
       <c r="C251">
@@ -11949,7 +11937,7 @@
       <c r="A252" t="s">
         <v>7</v>
       </c>
-      <c r="B252" s="4" t="s">
+      <c r="B252" s="3" t="s">
         <v>518</v>
       </c>
       <c r="C252">
@@ -11969,7 +11957,7 @@
       <c r="A253" t="s">
         <v>7</v>
       </c>
-      <c r="B253" s="4" t="s">
+      <c r="B253" s="3" t="s">
         <v>520</v>
       </c>
       <c r="C253">
@@ -11989,7 +11977,7 @@
       <c r="A254" t="s">
         <v>7</v>
       </c>
-      <c r="B254" s="4" t="s">
+      <c r="B254" s="3" t="s">
         <v>522</v>
       </c>
       <c r="C254">
@@ -12009,7 +11997,7 @@
       <c r="A255" t="s">
         <v>7</v>
       </c>
-      <c r="B255" s="4" t="s">
+      <c r="B255" s="3" t="s">
         <v>524</v>
       </c>
       <c r="C255">
@@ -12029,7 +12017,7 @@
       <c r="A256" t="s">
         <v>7</v>
       </c>
-      <c r="B256" s="4" t="s">
+      <c r="B256" s="3" t="s">
         <v>526</v>
       </c>
       <c r="C256">
@@ -12052,7 +12040,7 @@
       <c r="A257" t="s">
         <v>7</v>
       </c>
-      <c r="B257" s="4" t="s">
+      <c r="B257" s="3" t="s">
         <v>528</v>
       </c>
       <c r="C257">
@@ -12072,7 +12060,7 @@
       <c r="A258" t="s">
         <v>7</v>
       </c>
-      <c r="B258" s="4" t="s">
+      <c r="B258" s="3" t="s">
         <v>530</v>
       </c>
       <c r="C258">
@@ -12092,7 +12080,7 @@
       <c r="A259" t="s">
         <v>7</v>
       </c>
-      <c r="B259" s="4" t="s">
+      <c r="B259" s="3" t="s">
         <v>532</v>
       </c>
       <c r="C259">
@@ -12112,7 +12100,7 @@
       <c r="A260" t="s">
         <v>7</v>
       </c>
-      <c r="B260" s="4" t="s">
+      <c r="B260" s="3" t="s">
         <v>534</v>
       </c>
       <c r="C260">
@@ -12132,7 +12120,7 @@
       <c r="A261" t="s">
         <v>7</v>
       </c>
-      <c r="B261" s="4" t="s">
+      <c r="B261" s="3" t="s">
         <v>536</v>
       </c>
       <c r="C261">
@@ -12155,7 +12143,7 @@
       <c r="A262" t="s">
         <v>7</v>
       </c>
-      <c r="B262" s="4" t="s">
+      <c r="B262" s="3" t="s">
         <v>538</v>
       </c>
       <c r="C262">
@@ -12178,7 +12166,7 @@
       <c r="A263" t="s">
         <v>7</v>
       </c>
-      <c r="B263" s="4" t="s">
+      <c r="B263" s="3" t="s">
         <v>540</v>
       </c>
       <c r="C263">
@@ -12198,7 +12186,7 @@
       <c r="A264" t="s">
         <v>7</v>
       </c>
-      <c r="B264" s="4" t="s">
+      <c r="B264" s="3" t="s">
         <v>542</v>
       </c>
       <c r="C264">
@@ -12211,14 +12199,14 @@
         <v>543</v>
       </c>
       <c r="F264" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>7</v>
       </c>
-      <c r="B265" s="4" t="s">
+      <c r="B265" s="3" t="s">
         <v>544</v>
       </c>
       <c r="C265">
@@ -12231,14 +12219,14 @@
         <v>545</v>
       </c>
       <c r="F265" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
         <v>7</v>
       </c>
-      <c r="B266" s="4" t="s">
+      <c r="B266" s="3" t="s">
         <v>546</v>
       </c>
       <c r="C266">
@@ -12258,7 +12246,7 @@
       <c r="A267" t="s">
         <v>7</v>
       </c>
-      <c r="B267" s="4" t="s">
+      <c r="B267" s="3" t="s">
         <v>548</v>
       </c>
       <c r="C267">
@@ -12281,7 +12269,7 @@
       <c r="A268" t="s">
         <v>7</v>
       </c>
-      <c r="B268" s="4" t="s">
+      <c r="B268" s="3" t="s">
         <v>550</v>
       </c>
       <c r="C268">
@@ -12296,15 +12284,12 @@
       <c r="F268" t="s">
         <v>17</v>
       </c>
-      <c r="G268" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
         <v>7</v>
       </c>
-      <c r="B269" s="4" t="s">
+      <c r="B269" s="3" t="s">
         <v>552</v>
       </c>
       <c r="C269">
@@ -12317,14 +12302,14 @@
         <v>553</v>
       </c>
       <c r="F269" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
         <v>7</v>
       </c>
-      <c r="B270" s="4" t="s">
+      <c r="B270" s="3" t="s">
         <v>554</v>
       </c>
       <c r="C270">
@@ -12339,12 +12324,15 @@
       <c r="F270" t="s">
         <v>17</v>
       </c>
+      <c r="G270" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
         <v>7</v>
       </c>
-      <c r="B271" s="4" t="s">
+      <c r="B271" s="3" t="s">
         <v>556</v>
       </c>
       <c r="C271">
@@ -12357,14 +12345,14 @@
         <v>557</v>
       </c>
       <c r="F271" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
         <v>7</v>
       </c>
-      <c r="B272" s="4" t="s">
+      <c r="B272" s="3" t="s">
         <v>558</v>
       </c>
       <c r="C272">
@@ -12380,11 +12368,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:7">
       <c r="A273" t="s">
         <v>7</v>
       </c>
-      <c r="B273" s="4" t="s">
+      <c r="B273" s="3" t="s">
         <v>560</v>
       </c>
       <c r="C273">
@@ -12400,11 +12388,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:7">
       <c r="A274" t="s">
         <v>7</v>
       </c>
-      <c r="B274" s="4" t="s">
+      <c r="B274" s="3" t="s">
         <v>562</v>
       </c>
       <c r="C274">
@@ -12420,11 +12408,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:7">
       <c r="A275" t="s">
         <v>7</v>
       </c>
-      <c r="B275" s="4" t="s">
+      <c r="B275" s="3" t="s">
         <v>564</v>
       </c>
       <c r="C275">
@@ -12440,11 +12428,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:7">
       <c r="A276" t="s">
         <v>7</v>
       </c>
-      <c r="B276" s="4" t="s">
+      <c r="B276" s="3" t="s">
         <v>566</v>
       </c>
       <c r="C276">
@@ -12460,11 +12448,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
         <v>7</v>
       </c>
-      <c r="B277" s="4" t="s">
+      <c r="B277" s="3" t="s">
         <v>568</v>
       </c>
       <c r="C277">
@@ -12479,13 +12467,12 @@
       <c r="F277" t="s">
         <v>85</v>
       </c>
-      <c r="H277" s="3"/>
-    </row>
-    <row r="278" spans="1:8">
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
         <v>7</v>
       </c>
-      <c r="B278" s="4" t="s">
+      <c r="B278" s="3" t="s">
         <v>570</v>
       </c>
       <c r="C278">
@@ -12501,11 +12488,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
         <v>7</v>
       </c>
-      <c r="B279" s="4" t="s">
+      <c r="B279" s="3" t="s">
         <v>572</v>
       </c>
       <c r="C279">
@@ -12521,11 +12508,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
         <v>7</v>
       </c>
-      <c r="B280" s="4" t="s">
+      <c r="B280" s="3" t="s">
         <v>574</v>
       </c>
       <c r="C280">
@@ -12541,11 +12528,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:7">
       <c r="A281" t="s">
         <v>7</v>
       </c>
-      <c r="B281" s="4" t="s">
+      <c r="B281" s="3" t="s">
         <v>576</v>
       </c>
       <c r="C281">
@@ -12555,17 +12542,17 @@
         <v>30</v>
       </c>
       <c r="E281" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F281" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
         <v>7</v>
       </c>
-      <c r="B282" s="4" t="s">
+      <c r="B282" s="3" t="s">
         <v>577</v>
       </c>
       <c r="C282">
@@ -12581,11 +12568,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
         <v>7</v>
       </c>
-      <c r="B283" s="4" t="s">
+      <c r="B283" s="3" t="s">
         <v>579</v>
       </c>
       <c r="C283">
@@ -12601,11 +12588,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:7">
       <c r="A284" t="s">
         <v>7</v>
       </c>
-      <c r="B284" s="4" t="s">
+      <c r="B284" s="3" t="s">
         <v>581</v>
       </c>
       <c r="C284">
@@ -12621,11 +12608,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" spans="1:7">
       <c r="A285" t="s">
         <v>7</v>
       </c>
-      <c r="B285" s="4" t="s">
+      <c r="B285" s="3" t="s">
         <v>583</v>
       </c>
       <c r="C285">
@@ -12641,11 +12628,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:7">
       <c r="A286" t="s">
         <v>7</v>
       </c>
-      <c r="B286" s="4" t="s">
+      <c r="B286" s="3" t="s">
         <v>585</v>
       </c>
       <c r="C286">
@@ -12661,11 +12648,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:7">
       <c r="A287" t="s">
         <v>7</v>
       </c>
-      <c r="B287" s="4" t="s">
+      <c r="B287" s="3" t="s">
         <v>587</v>
       </c>
       <c r="C287">
@@ -12684,11 +12671,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="288" spans="1:8">
+    <row r="288" spans="1:7">
       <c r="A288" t="s">
         <v>7</v>
       </c>
-      <c r="B288" s="4" t="s">
+      <c r="B288" s="3" t="s">
         <v>589</v>
       </c>
       <c r="C288">
@@ -12711,7 +12698,7 @@
       <c r="A289" t="s">
         <v>7</v>
       </c>
-      <c r="B289" s="4" t="s">
+      <c r="B289" s="3" t="s">
         <v>591</v>
       </c>
       <c r="C289">
@@ -12734,7 +12721,7 @@
       <c r="A290" t="s">
         <v>7</v>
       </c>
-      <c r="B290" s="4" t="s">
+      <c r="B290" s="3" t="s">
         <v>593</v>
       </c>
       <c r="C290">
@@ -12757,7 +12744,7 @@
       <c r="A291" t="s">
         <v>7</v>
       </c>
-      <c r="B291" s="4" t="s">
+      <c r="B291" s="3" t="s">
         <v>595</v>
       </c>
       <c r="C291">
@@ -12780,7 +12767,7 @@
       <c r="A292" t="s">
         <v>7</v>
       </c>
-      <c r="B292" s="4" t="s">
+      <c r="B292" s="3" t="s">
         <v>597</v>
       </c>
       <c r="C292">
@@ -12803,7 +12790,7 @@
       <c r="A293" t="s">
         <v>7</v>
       </c>
-      <c r="B293" s="4" t="s">
+      <c r="B293" s="3" t="s">
         <v>599</v>
       </c>
       <c r="C293">
@@ -12826,7 +12813,7 @@
       <c r="A294" t="s">
         <v>7</v>
       </c>
-      <c r="B294" s="4" t="s">
+      <c r="B294" s="3" t="s">
         <v>601</v>
       </c>
       <c r="C294">
@@ -12846,7 +12833,7 @@
       <c r="A295" t="s">
         <v>7</v>
       </c>
-      <c r="B295" s="4" t="s">
+      <c r="B295" s="3" t="s">
         <v>603</v>
       </c>
       <c r="C295">
@@ -12866,7 +12853,7 @@
       <c r="A296" t="s">
         <v>7</v>
       </c>
-      <c r="B296" s="4" t="s">
+      <c r="B296" s="3" t="s">
         <v>605</v>
       </c>
       <c r="C296">
@@ -12889,7 +12876,7 @@
       <c r="A297" t="s">
         <v>7</v>
       </c>
-      <c r="B297" s="4" t="s">
+      <c r="B297" s="3" t="s">
         <v>607</v>
       </c>
       <c r="C297">
@@ -12912,7 +12899,7 @@
       <c r="A298" t="s">
         <v>7</v>
       </c>
-      <c r="B298" s="4" t="s">
+      <c r="B298" s="3" t="s">
         <v>609</v>
       </c>
       <c r="C298">
@@ -12935,7 +12922,7 @@
       <c r="A299" t="s">
         <v>7</v>
       </c>
-      <c r="B299" s="4" t="s">
+      <c r="B299" s="3" t="s">
         <v>611</v>
       </c>
       <c r="C299">
@@ -12955,7 +12942,7 @@
       <c r="A300" t="s">
         <v>7</v>
       </c>
-      <c r="B300" s="4" t="s">
+      <c r="B300" s="3" t="s">
         <v>613</v>
       </c>
       <c r="C300">
@@ -12975,7 +12962,7 @@
       <c r="A301" t="s">
         <v>7</v>
       </c>
-      <c r="B301" s="4" t="s">
+      <c r="B301" s="3" t="s">
         <v>615</v>
       </c>
       <c r="C301">
@@ -12998,7 +12985,7 @@
       <c r="A302" t="s">
         <v>7</v>
       </c>
-      <c r="B302" s="4" t="s">
+      <c r="B302" s="3" t="s">
         <v>617</v>
       </c>
       <c r="C302">
@@ -13021,7 +13008,7 @@
       <c r="A303" t="s">
         <v>7</v>
       </c>
-      <c r="B303" s="4" t="s">
+      <c r="B303" s="3" t="s">
         <v>619</v>
       </c>
       <c r="C303">
@@ -13044,7 +13031,7 @@
       <c r="A304" t="s">
         <v>7</v>
       </c>
-      <c r="B304" s="4" t="s">
+      <c r="B304" s="3" t="s">
         <v>621</v>
       </c>
       <c r="C304">
@@ -13064,7 +13051,7 @@
       <c r="A305" t="s">
         <v>7</v>
       </c>
-      <c r="B305" s="4" t="s">
+      <c r="B305" s="3" t="s">
         <v>623</v>
       </c>
       <c r="C305">
@@ -13087,7 +13074,7 @@
       <c r="A306" t="s">
         <v>7</v>
       </c>
-      <c r="B306" s="4" t="s">
+      <c r="B306" s="3" t="s">
         <v>625</v>
       </c>
       <c r="C306">
@@ -13110,7 +13097,7 @@
       <c r="A307" t="s">
         <v>7</v>
       </c>
-      <c r="B307" s="4" t="s">
+      <c r="B307" s="3" t="s">
         <v>627</v>
       </c>
       <c r="C307">
@@ -13133,7 +13120,7 @@
       <c r="A308" t="s">
         <v>7</v>
       </c>
-      <c r="B308" s="4" t="s">
+      <c r="B308" s="3" t="s">
         <v>629</v>
       </c>
       <c r="C308">
@@ -13156,7 +13143,7 @@
       <c r="A309" t="s">
         <v>7</v>
       </c>
-      <c r="B309" s="4" t="s">
+      <c r="B309" s="3" t="s">
         <v>631</v>
       </c>
       <c r="C309">
@@ -13176,7 +13163,7 @@
       <c r="A310" t="s">
         <v>7</v>
       </c>
-      <c r="B310" s="4" t="s">
+      <c r="B310" s="3" t="s">
         <v>633</v>
       </c>
       <c r="C310">
@@ -13196,7 +13183,7 @@
       <c r="A311" t="s">
         <v>7</v>
       </c>
-      <c r="B311" s="4" t="s">
+      <c r="B311" s="3" t="s">
         <v>635</v>
       </c>
       <c r="C311">
@@ -13216,7 +13203,7 @@
       <c r="A312" t="s">
         <v>7</v>
       </c>
-      <c r="B312" s="4" t="s">
+      <c r="B312" s="3" t="s">
         <v>637</v>
       </c>
       <c r="C312">
@@ -13236,7 +13223,7 @@
       <c r="A313" t="s">
         <v>7</v>
       </c>
-      <c r="B313" s="4" t="s">
+      <c r="B313" s="3" t="s">
         <v>639</v>
       </c>
       <c r="C313">
@@ -13259,7 +13246,7 @@
       <c r="A314" t="s">
         <v>7</v>
       </c>
-      <c r="B314" s="4" t="s">
+      <c r="B314" s="3" t="s">
         <v>641</v>
       </c>
       <c r="C314">
@@ -13279,7 +13266,7 @@
       <c r="A315" t="s">
         <v>7</v>
       </c>
-      <c r="B315" s="4" t="s">
+      <c r="B315" s="3" t="s">
         <v>643</v>
       </c>
       <c r="C315">
@@ -13299,7 +13286,7 @@
       <c r="A316" t="s">
         <v>7</v>
       </c>
-      <c r="B316" s="4" t="s">
+      <c r="B316" s="3" t="s">
         <v>645</v>
       </c>
       <c r="C316">
@@ -13322,7 +13309,7 @@
       <c r="A317" t="s">
         <v>7</v>
       </c>
-      <c r="B317" s="4" t="s">
+      <c r="B317" s="3" t="s">
         <v>647</v>
       </c>
       <c r="C317">
@@ -13342,7 +13329,7 @@
       <c r="A318" t="s">
         <v>7</v>
       </c>
-      <c r="B318" s="4" t="s">
+      <c r="B318" s="3" t="s">
         <v>649</v>
       </c>
       <c r="C318">
@@ -13365,7 +13352,7 @@
       <c r="A319" t="s">
         <v>7</v>
       </c>
-      <c r="B319" s="4" t="s">
+      <c r="B319" s="3" t="s">
         <v>651</v>
       </c>
       <c r="C319">
@@ -13388,7 +13375,7 @@
       <c r="A320" t="s">
         <v>7</v>
       </c>
-      <c r="B320" s="4" t="s">
+      <c r="B320" s="3" t="s">
         <v>653</v>
       </c>
       <c r="C320">
@@ -13408,7 +13395,7 @@
       <c r="A321" t="s">
         <v>7</v>
       </c>
-      <c r="B321" s="4" t="s">
+      <c r="B321" s="3" t="s">
         <v>655</v>
       </c>
       <c r="C321">
@@ -13428,7 +13415,7 @@
       <c r="A322" t="s">
         <v>7</v>
       </c>
-      <c r="B322" s="4" t="s">
+      <c r="B322" s="3" t="s">
         <v>657</v>
       </c>
       <c r="C322">
@@ -13448,7 +13435,7 @@
       <c r="A323" t="s">
         <v>7</v>
       </c>
-      <c r="B323" s="4" t="s">
+      <c r="B323" s="3" t="s">
         <v>659</v>
       </c>
       <c r="C323">
@@ -13468,7 +13455,7 @@
       <c r="A324" t="s">
         <v>7</v>
       </c>
-      <c r="B324" s="4" t="s">
+      <c r="B324" s="3" t="s">
         <v>661</v>
       </c>
       <c r="C324">
@@ -13488,7 +13475,7 @@
       <c r="A325" t="s">
         <v>7</v>
       </c>
-      <c r="B325" s="4" t="s">
+      <c r="B325" s="3" t="s">
         <v>663</v>
       </c>
       <c r="C325">
@@ -13508,7 +13495,7 @@
       <c r="A326" t="s">
         <v>7</v>
       </c>
-      <c r="B326" s="4" t="s">
+      <c r="B326" s="3" t="s">
         <v>665</v>
       </c>
       <c r="C326">
@@ -13528,7 +13515,7 @@
       <c r="A327" t="s">
         <v>7</v>
       </c>
-      <c r="B327" s="4" t="s">
+      <c r="B327" s="3" t="s">
         <v>667</v>
       </c>
       <c r="C327">
@@ -13548,7 +13535,7 @@
       <c r="A328" t="s">
         <v>7</v>
       </c>
-      <c r="B328" s="4" t="s">
+      <c r="B328" s="3" t="s">
         <v>669</v>
       </c>
       <c r="C328">
@@ -13571,7 +13558,7 @@
       <c r="A329" t="s">
         <v>7</v>
       </c>
-      <c r="B329" s="4" t="s">
+      <c r="B329" s="3" t="s">
         <v>671</v>
       </c>
       <c r="C329">
@@ -13591,7 +13578,7 @@
       <c r="A330" t="s">
         <v>7</v>
       </c>
-      <c r="B330" s="4" t="s">
+      <c r="B330" s="3" t="s">
         <v>673</v>
       </c>
       <c r="C330">
@@ -13611,7 +13598,7 @@
       <c r="A331" t="s">
         <v>7</v>
       </c>
-      <c r="B331" s="4" t="s">
+      <c r="B331" s="3" t="s">
         <v>675</v>
       </c>
       <c r="C331">
@@ -13634,7 +13621,7 @@
       <c r="A332" t="s">
         <v>7</v>
       </c>
-      <c r="B332" s="4" t="s">
+      <c r="B332" s="3" t="s">
         <v>677</v>
       </c>
       <c r="C332">
@@ -13657,7 +13644,7 @@
       <c r="A333" t="s">
         <v>7</v>
       </c>
-      <c r="B333" s="4" t="s">
+      <c r="B333" s="3" t="s">
         <v>679</v>
       </c>
       <c r="C333">
@@ -13680,7 +13667,7 @@
       <c r="A334" t="s">
         <v>7</v>
       </c>
-      <c r="B334" s="4" t="s">
+      <c r="B334" s="3" t="s">
         <v>681</v>
       </c>
       <c r="C334">
@@ -13700,7 +13687,7 @@
       <c r="A335" t="s">
         <v>7</v>
       </c>
-      <c r="B335" s="4" t="s">
+      <c r="B335" s="3" t="s">
         <v>683</v>
       </c>
       <c r="C335">
@@ -13720,7 +13707,7 @@
       <c r="A336" t="s">
         <v>685</v>
       </c>
-      <c r="B336" s="4" t="s">
+      <c r="B336" s="3" t="s">
         <v>686</v>
       </c>
       <c r="C336">
@@ -13743,7 +13730,7 @@
       <c r="A337" t="s">
         <v>685</v>
       </c>
-      <c r="B337" s="4" t="s">
+      <c r="B337" s="3" t="s">
         <v>688</v>
       </c>
       <c r="C337">
@@ -13763,7 +13750,7 @@
       <c r="A338" t="s">
         <v>685</v>
       </c>
-      <c r="B338" s="4" t="s">
+      <c r="B338" s="3" t="s">
         <v>690</v>
       </c>
       <c r="C338">
@@ -13786,7 +13773,7 @@
       <c r="A339" t="s">
         <v>685</v>
       </c>
-      <c r="B339" s="4" t="s">
+      <c r="B339" s="3" t="s">
         <v>692</v>
       </c>
       <c r="C339">
@@ -13809,7 +13796,7 @@
       <c r="A340" t="s">
         <v>685</v>
       </c>
-      <c r="B340" s="4" t="s">
+      <c r="B340" s="3" t="s">
         <v>694</v>
       </c>
       <c r="C340">
@@ -13829,7 +13816,7 @@
       <c r="A341" t="s">
         <v>685</v>
       </c>
-      <c r="B341" s="4" t="s">
+      <c r="B341" s="3" t="s">
         <v>696</v>
       </c>
       <c r="C341">
@@ -13849,7 +13836,7 @@
       <c r="A342" t="s">
         <v>685</v>
       </c>
-      <c r="B342" s="4" t="s">
+      <c r="B342" s="3" t="s">
         <v>698</v>
       </c>
       <c r="C342">
@@ -13869,7 +13856,7 @@
       <c r="A343" t="s">
         <v>685</v>
       </c>
-      <c r="B343" s="4" t="s">
+      <c r="B343" s="3" t="s">
         <v>700</v>
       </c>
       <c r="C343">
@@ -13889,7 +13876,7 @@
       <c r="A344" t="s">
         <v>685</v>
       </c>
-      <c r="B344" s="4" t="s">
+      <c r="B344" s="3" t="s">
         <v>702</v>
       </c>
       <c r="C344">
@@ -13909,7 +13896,7 @@
       <c r="A345" t="s">
         <v>685</v>
       </c>
-      <c r="B345" s="4" t="s">
+      <c r="B345" s="3" t="s">
         <v>704</v>
       </c>
       <c r="C345">
@@ -13929,7 +13916,7 @@
       <c r="A346" t="s">
         <v>685</v>
       </c>
-      <c r="B346" s="4" t="s">
+      <c r="B346" s="3" t="s">
         <v>706</v>
       </c>
       <c r="C346">
@@ -13949,7 +13936,7 @@
       <c r="A347" t="s">
         <v>685</v>
       </c>
-      <c r="B347" s="4" t="s">
+      <c r="B347" s="3" t="s">
         <v>708</v>
       </c>
       <c r="C347">
@@ -13972,7 +13959,7 @@
       <c r="A348" t="s">
         <v>685</v>
       </c>
-      <c r="B348" s="4" t="s">
+      <c r="B348" s="3" t="s">
         <v>710</v>
       </c>
       <c r="C348">
@@ -13995,7 +13982,7 @@
       <c r="A349" t="s">
         <v>685</v>
       </c>
-      <c r="B349" s="4" t="s">
+      <c r="B349" s="3" t="s">
         <v>711</v>
       </c>
       <c r="C349">
@@ -14015,7 +14002,7 @@
       <c r="A350" t="s">
         <v>685</v>
       </c>
-      <c r="B350" s="4" t="s">
+      <c r="B350" s="3" t="s">
         <v>713</v>
       </c>
       <c r="C350">
@@ -14035,7 +14022,7 @@
       <c r="A351" t="s">
         <v>685</v>
       </c>
-      <c r="B351" s="4" t="s">
+      <c r="B351" s="3" t="s">
         <v>715</v>
       </c>
       <c r="C351">
@@ -14055,7 +14042,7 @@
       <c r="A352" t="s">
         <v>685</v>
       </c>
-      <c r="B352" s="4" t="s">
+      <c r="B352" s="3" t="s">
         <v>717</v>
       </c>
       <c r="C352">
@@ -14078,7 +14065,7 @@
       <c r="A353" t="s">
         <v>685</v>
       </c>
-      <c r="B353" s="4" t="s">
+      <c r="B353" s="3" t="s">
         <v>719</v>
       </c>
       <c r="C353">
@@ -14101,7 +14088,7 @@
       <c r="A354" t="s">
         <v>685</v>
       </c>
-      <c r="B354" s="4" t="s">
+      <c r="B354" s="3" t="s">
         <v>721</v>
       </c>
       <c r="C354">
@@ -14124,7 +14111,7 @@
       <c r="A355" t="s">
         <v>685</v>
       </c>
-      <c r="B355" s="4" t="s">
+      <c r="B355" s="3" t="s">
         <v>723</v>
       </c>
       <c r="C355">
@@ -14144,7 +14131,7 @@
       <c r="A356" t="s">
         <v>685</v>
       </c>
-      <c r="B356" s="4" t="s">
+      <c r="B356" s="3" t="s">
         <v>725</v>
       </c>
       <c r="C356">
@@ -14164,7 +14151,7 @@
       <c r="A357" t="s">
         <v>685</v>
       </c>
-      <c r="B357" s="4" t="s">
+      <c r="B357" s="3" t="s">
         <v>727</v>
       </c>
       <c r="C357">
@@ -14184,7 +14171,7 @@
       <c r="A358" t="s">
         <v>685</v>
       </c>
-      <c r="B358" s="4" t="s">
+      <c r="B358" s="3" t="s">
         <v>729</v>
       </c>
       <c r="C358">
@@ -14204,7 +14191,7 @@
       <c r="A359" t="s">
         <v>685</v>
       </c>
-      <c r="B359" s="4" t="s">
+      <c r="B359" s="3" t="s">
         <v>731</v>
       </c>
       <c r="C359">
@@ -14224,7 +14211,7 @@
       <c r="A360" t="s">
         <v>685</v>
       </c>
-      <c r="B360" s="4" t="s">
+      <c r="B360" s="3" t="s">
         <v>733</v>
       </c>
       <c r="C360">
@@ -14244,7 +14231,7 @@
       <c r="A361" t="s">
         <v>685</v>
       </c>
-      <c r="B361" s="4" t="s">
+      <c r="B361" s="3" t="s">
         <v>735</v>
       </c>
       <c r="C361">
@@ -14264,7 +14251,7 @@
       <c r="A362" t="s">
         <v>685</v>
       </c>
-      <c r="B362" s="4" t="s">
+      <c r="B362" s="3" t="s">
         <v>737</v>
       </c>
       <c r="C362">
@@ -14287,7 +14274,7 @@
       <c r="A363" t="s">
         <v>685</v>
       </c>
-      <c r="B363" s="4" t="s">
+      <c r="B363" s="3" t="s">
         <v>739</v>
       </c>
       <c r="C363">
@@ -14307,7 +14294,7 @@
       <c r="A364" t="s">
         <v>685</v>
       </c>
-      <c r="B364" s="4" t="s">
+      <c r="B364" s="3" t="s">
         <v>741</v>
       </c>
       <c r="C364">
@@ -14327,7 +14314,7 @@
       <c r="A365" t="s">
         <v>685</v>
       </c>
-      <c r="B365" s="4" t="s">
+      <c r="B365" s="3" t="s">
         <v>743</v>
       </c>
       <c r="C365">
@@ -14350,7 +14337,7 @@
       <c r="A366" t="s">
         <v>685</v>
       </c>
-      <c r="B366" s="4" t="s">
+      <c r="B366" s="3" t="s">
         <v>745</v>
       </c>
       <c r="C366">
@@ -14370,7 +14357,7 @@
       <c r="A367" t="s">
         <v>685</v>
       </c>
-      <c r="B367" s="4" t="s">
+      <c r="B367" s="3" t="s">
         <v>747</v>
       </c>
       <c r="C367">
@@ -14390,7 +14377,7 @@
       <c r="A368" t="s">
         <v>685</v>
       </c>
-      <c r="B368" s="4" t="s">
+      <c r="B368" s="3" t="s">
         <v>749</v>
       </c>
       <c r="C368">
@@ -14413,7 +14400,7 @@
       <c r="A369" t="s">
         <v>685</v>
       </c>
-      <c r="B369" s="4" t="s">
+      <c r="B369" s="3" t="s">
         <v>751</v>
       </c>
       <c r="C369">
@@ -14433,7 +14420,7 @@
       <c r="A370" t="s">
         <v>685</v>
       </c>
-      <c r="B370" s="4" t="s">
+      <c r="B370" s="3" t="s">
         <v>753</v>
       </c>
       <c r="C370">
@@ -14456,7 +14443,7 @@
       <c r="A371" t="s">
         <v>685</v>
       </c>
-      <c r="B371" s="4" t="s">
+      <c r="B371" s="3" t="s">
         <v>755</v>
       </c>
       <c r="C371">
@@ -14476,7 +14463,7 @@
       <c r="A372" t="s">
         <v>685</v>
       </c>
-      <c r="B372" s="4" t="s">
+      <c r="B372" s="3" t="s">
         <v>757</v>
       </c>
       <c r="C372">
@@ -14496,7 +14483,7 @@
       <c r="A373" t="s">
         <v>685</v>
       </c>
-      <c r="B373" s="4" t="s">
+      <c r="B373" s="3" t="s">
         <v>759</v>
       </c>
       <c r="C373">
@@ -14519,7 +14506,7 @@
       <c r="A374" t="s">
         <v>685</v>
       </c>
-      <c r="B374" s="4" t="s">
+      <c r="B374" s="3" t="s">
         <v>761</v>
       </c>
       <c r="C374">
@@ -14539,7 +14526,7 @@
       <c r="A375" t="s">
         <v>685</v>
       </c>
-      <c r="B375" s="4" t="s">
+      <c r="B375" s="3" t="s">
         <v>763</v>
       </c>
       <c r="C375">
@@ -14559,7 +14546,7 @@
       <c r="A376" t="s">
         <v>685</v>
       </c>
-      <c r="B376" s="4" t="s">
+      <c r="B376" s="3" t="s">
         <v>765</v>
       </c>
       <c r="C376">
@@ -14582,7 +14569,7 @@
       <c r="A377" t="s">
         <v>685</v>
       </c>
-      <c r="B377" s="4" t="s">
+      <c r="B377" s="3" t="s">
         <v>767</v>
       </c>
       <c r="C377">
@@ -14602,7 +14589,7 @@
       <c r="A378" t="s">
         <v>685</v>
       </c>
-      <c r="B378" s="4" t="s">
+      <c r="B378" s="3" t="s">
         <v>769</v>
       </c>
       <c r="C378">
@@ -14625,7 +14612,7 @@
       <c r="A379" t="s">
         <v>685</v>
       </c>
-      <c r="B379" s="4" t="s">
+      <c r="B379" s="3" t="s">
         <v>771</v>
       </c>
       <c r="C379">
@@ -14648,7 +14635,7 @@
       <c r="A380" t="s">
         <v>685</v>
       </c>
-      <c r="B380" s="4" t="s">
+      <c r="B380" s="3" t="s">
         <v>773</v>
       </c>
       <c r="C380">
@@ -14668,7 +14655,7 @@
       <c r="A381" t="s">
         <v>685</v>
       </c>
-      <c r="B381" s="4" t="s">
+      <c r="B381" s="3" t="s">
         <v>775</v>
       </c>
       <c r="C381">
@@ -14688,7 +14675,7 @@
       <c r="A382" t="s">
         <v>685</v>
       </c>
-      <c r="B382" s="4" t="s">
+      <c r="B382" s="3" t="s">
         <v>777</v>
       </c>
       <c r="C382">
@@ -14708,7 +14695,7 @@
       <c r="A383" t="s">
         <v>685</v>
       </c>
-      <c r="B383" s="4" t="s">
+      <c r="B383" s="3" t="s">
         <v>779</v>
       </c>
       <c r="C383">
@@ -14728,7 +14715,7 @@
       <c r="A384" t="s">
         <v>685</v>
       </c>
-      <c r="B384" s="4" t="s">
+      <c r="B384" s="3" t="s">
         <v>781</v>
       </c>
       <c r="C384">
@@ -14748,7 +14735,7 @@
       <c r="A385" t="s">
         <v>685</v>
       </c>
-      <c r="B385" s="4" t="s">
+      <c r="B385" s="3" t="s">
         <v>783</v>
       </c>
       <c r="C385">
@@ -14771,7 +14758,7 @@
       <c r="A386" t="s">
         <v>685</v>
       </c>
-      <c r="B386" s="4" t="s">
+      <c r="B386" s="3" t="s">
         <v>785</v>
       </c>
       <c r="C386">
@@ -14791,7 +14778,7 @@
       <c r="A387" t="s">
         <v>685</v>
       </c>
-      <c r="B387" s="4" t="s">
+      <c r="B387" s="3" t="s">
         <v>787</v>
       </c>
       <c r="C387">
@@ -14814,7 +14801,7 @@
       <c r="A388" t="s">
         <v>685</v>
       </c>
-      <c r="B388" s="4" t="s">
+      <c r="B388" s="3" t="s">
         <v>789</v>
       </c>
       <c r="C388">
@@ -14837,7 +14824,7 @@
       <c r="A389" t="s">
         <v>685</v>
       </c>
-      <c r="B389" s="4" t="s">
+      <c r="B389" s="3" t="s">
         <v>791</v>
       </c>
       <c r="C389">
@@ -14857,7 +14844,7 @@
       <c r="A390" t="s">
         <v>685</v>
       </c>
-      <c r="B390" s="4" t="s">
+      <c r="B390" s="3" t="s">
         <v>793</v>
       </c>
       <c r="C390">
@@ -14877,7 +14864,7 @@
       <c r="A391" t="s">
         <v>685</v>
       </c>
-      <c r="B391" s="4" t="s">
+      <c r="B391" s="3" t="s">
         <v>795</v>
       </c>
       <c r="C391">
@@ -14900,7 +14887,7 @@
       <c r="A392" t="s">
         <v>685</v>
       </c>
-      <c r="B392" s="4" t="s">
+      <c r="B392" s="3" t="s">
         <v>797</v>
       </c>
       <c r="C392">
@@ -14923,7 +14910,7 @@
       <c r="A393" t="s">
         <v>685</v>
       </c>
-      <c r="B393" s="4" t="s">
+      <c r="B393" s="3" t="s">
         <v>799</v>
       </c>
       <c r="C393">
@@ -14943,7 +14930,7 @@
       <c r="A394" t="s">
         <v>685</v>
       </c>
-      <c r="B394" s="4" t="s">
+      <c r="B394" s="3" t="s">
         <v>801</v>
       </c>
       <c r="C394">
@@ -14963,7 +14950,7 @@
       <c r="A395" t="s">
         <v>685</v>
       </c>
-      <c r="B395" s="4" t="s">
+      <c r="B395" s="3" t="s">
         <v>803</v>
       </c>
       <c r="C395">
@@ -14983,7 +14970,7 @@
       <c r="A396" t="s">
         <v>685</v>
       </c>
-      <c r="B396" s="4" t="s">
+      <c r="B396" s="3" t="s">
         <v>805</v>
       </c>
       <c r="C396">
@@ -15003,7 +14990,7 @@
       <c r="A397" t="s">
         <v>685</v>
       </c>
-      <c r="B397" s="4" t="s">
+      <c r="B397" s="3" t="s">
         <v>807</v>
       </c>
       <c r="C397">
@@ -15023,7 +15010,7 @@
       <c r="A398" t="s">
         <v>685</v>
       </c>
-      <c r="B398" s="4" t="s">
+      <c r="B398" s="3" t="s">
         <v>809</v>
       </c>
       <c r="C398">
@@ -15043,7 +15030,7 @@
       <c r="A399" t="s">
         <v>685</v>
       </c>
-      <c r="B399" s="4" t="s">
+      <c r="B399" s="3" t="s">
         <v>811</v>
       </c>
       <c r="C399">
@@ -15063,7 +15050,7 @@
       <c r="A400" t="s">
         <v>685</v>
       </c>
-      <c r="B400" s="4" t="s">
+      <c r="B400" s="3" t="s">
         <v>813</v>
       </c>
       <c r="C400">
@@ -15083,7 +15070,7 @@
       <c r="A401" t="s">
         <v>685</v>
       </c>
-      <c r="B401" s="4" t="s">
+      <c r="B401" s="3" t="s">
         <v>815</v>
       </c>
       <c r="C401">
@@ -15106,7 +15093,7 @@
       <c r="A402" t="s">
         <v>685</v>
       </c>
-      <c r="B402" s="4" t="s">
+      <c r="B402" s="3" t="s">
         <v>817</v>
       </c>
       <c r="C402">
@@ -15126,7 +15113,7 @@
       <c r="A403" t="s">
         <v>685</v>
       </c>
-      <c r="B403" s="4" t="s">
+      <c r="B403" s="3" t="s">
         <v>819</v>
       </c>
       <c r="C403">
@@ -15149,7 +15136,7 @@
       <c r="A404" t="s">
         <v>685</v>
       </c>
-      <c r="B404" s="4" t="s">
+      <c r="B404" s="3" t="s">
         <v>821</v>
       </c>
       <c r="C404">
@@ -15169,7 +15156,7 @@
       <c r="A405" t="s">
         <v>685</v>
       </c>
-      <c r="B405" s="4" t="s">
+      <c r="B405" s="3" t="s">
         <v>823</v>
       </c>
       <c r="C405">
@@ -15192,7 +15179,7 @@
       <c r="A406" t="s">
         <v>685</v>
       </c>
-      <c r="B406" s="4" t="s">
+      <c r="B406" s="3" t="s">
         <v>825</v>
       </c>
       <c r="C406">
@@ -15215,7 +15202,7 @@
       <c r="A407" t="s">
         <v>685</v>
       </c>
-      <c r="B407" s="4" t="s">
+      <c r="B407" s="3" t="s">
         <v>827</v>
       </c>
       <c r="C407">
@@ -15238,7 +15225,7 @@
       <c r="A408" t="s">
         <v>685</v>
       </c>
-      <c r="B408" s="4" t="s">
+      <c r="B408" s="3" t="s">
         <v>829</v>
       </c>
       <c r="C408">
@@ -15261,7 +15248,7 @@
       <c r="A409" t="s">
         <v>685</v>
       </c>
-      <c r="B409" s="4" t="s">
+      <c r="B409" s="3" t="s">
         <v>831</v>
       </c>
       <c r="C409">
@@ -15281,7 +15268,7 @@
       <c r="A410" t="s">
         <v>685</v>
       </c>
-      <c r="B410" s="4" t="s">
+      <c r="B410" s="3" t="s">
         <v>833</v>
       </c>
       <c r="C410">
@@ -15304,7 +15291,7 @@
       <c r="A411" t="s">
         <v>685</v>
       </c>
-      <c r="B411" s="4" t="s">
+      <c r="B411" s="3" t="s">
         <v>835</v>
       </c>
       <c r="C411">
@@ -15327,7 +15314,7 @@
       <c r="A412" t="s">
         <v>685</v>
       </c>
-      <c r="B412" s="4" t="s">
+      <c r="B412" s="3" t="s">
         <v>837</v>
       </c>
       <c r="C412">
@@ -15347,7 +15334,7 @@
       <c r="A413" t="s">
         <v>685</v>
       </c>
-      <c r="B413" s="4" t="s">
+      <c r="B413" s="3" t="s">
         <v>839</v>
       </c>
       <c r="C413">
@@ -15370,7 +15357,7 @@
       <c r="A414" t="s">
         <v>685</v>
       </c>
-      <c r="B414" s="4" t="s">
+      <c r="B414" s="3" t="s">
         <v>841</v>
       </c>
       <c r="C414">
@@ -15393,7 +15380,7 @@
       <c r="A415" t="s">
         <v>685</v>
       </c>
-      <c r="B415" s="4" t="s">
+      <c r="B415" s="3" t="s">
         <v>843</v>
       </c>
       <c r="C415">
@@ -15413,7 +15400,7 @@
       <c r="A416" t="s">
         <v>685</v>
       </c>
-      <c r="B416" s="4" t="s">
+      <c r="B416" s="3" t="s">
         <v>845</v>
       </c>
       <c r="C416">
@@ -15436,7 +15423,7 @@
       <c r="A417" t="s">
         <v>685</v>
       </c>
-      <c r="B417" s="4" t="s">
+      <c r="B417" s="3" t="s">
         <v>847</v>
       </c>
       <c r="C417">
@@ -15459,7 +15446,7 @@
       <c r="A418" t="s">
         <v>685</v>
       </c>
-      <c r="B418" s="4" t="s">
+      <c r="B418" s="3" t="s">
         <v>849</v>
       </c>
       <c r="C418">
@@ -15482,7 +15469,7 @@
       <c r="A419" t="s">
         <v>685</v>
       </c>
-      <c r="B419" s="4" t="s">
+      <c r="B419" s="3" t="s">
         <v>851</v>
       </c>
       <c r="C419">
@@ -15502,7 +15489,7 @@
       <c r="A420" t="s">
         <v>685</v>
       </c>
-      <c r="B420" s="4" t="s">
+      <c r="B420" s="3" t="s">
         <v>853</v>
       </c>
       <c r="C420">
@@ -15525,7 +15512,7 @@
       <c r="A421" t="s">
         <v>685</v>
       </c>
-      <c r="B421" s="4" t="s">
+      <c r="B421" s="3" t="s">
         <v>855</v>
       </c>
       <c r="C421">
@@ -15548,7 +15535,7 @@
       <c r="A422" t="s">
         <v>685</v>
       </c>
-      <c r="B422" s="4" t="s">
+      <c r="B422" s="3" t="s">
         <v>857</v>
       </c>
       <c r="C422">
@@ -15571,7 +15558,7 @@
       <c r="A423" t="s">
         <v>685</v>
       </c>
-      <c r="B423" s="4" t="s">
+      <c r="B423" s="3" t="s">
         <v>859</v>
       </c>
       <c r="C423">
@@ -15594,7 +15581,7 @@
       <c r="A424" t="s">
         <v>685</v>
       </c>
-      <c r="B424" s="4" t="s">
+      <c r="B424" s="3" t="s">
         <v>861</v>
       </c>
       <c r="C424">
@@ -15617,7 +15604,7 @@
       <c r="A425" t="s">
         <v>685</v>
       </c>
-      <c r="B425" s="4" t="s">
+      <c r="B425" s="3" t="s">
         <v>863</v>
       </c>
       <c r="C425">
@@ -15637,7 +15624,7 @@
       <c r="A426" t="s">
         <v>685</v>
       </c>
-      <c r="B426" s="4" t="s">
+      <c r="B426" s="3" t="s">
         <v>865</v>
       </c>
       <c r="C426">
@@ -15657,7 +15644,7 @@
       <c r="A427" t="s">
         <v>685</v>
       </c>
-      <c r="B427" s="4" t="s">
+      <c r="B427" s="3" t="s">
         <v>867</v>
       </c>
       <c r="C427">
@@ -15677,7 +15664,7 @@
       <c r="A428" t="s">
         <v>685</v>
       </c>
-      <c r="B428" s="4" t="s">
+      <c r="B428" s="3" t="s">
         <v>869</v>
       </c>
       <c r="C428">
@@ -15697,7 +15684,7 @@
       <c r="A429" t="s">
         <v>685</v>
       </c>
-      <c r="B429" s="4" t="s">
+      <c r="B429" s="3" t="s">
         <v>871</v>
       </c>
       <c r="C429">
@@ -15717,7 +15704,7 @@
       <c r="A430" t="s">
         <v>685</v>
       </c>
-      <c r="B430" s="4" t="s">
+      <c r="B430" s="3" t="s">
         <v>873</v>
       </c>
       <c r="C430">
@@ -15737,7 +15724,7 @@
       <c r="A431" t="s">
         <v>685</v>
       </c>
-      <c r="B431" s="4" t="s">
+      <c r="B431" s="3" t="s">
         <v>875</v>
       </c>
       <c r="C431">
@@ -15757,7 +15744,7 @@
       <c r="A432" t="s">
         <v>685</v>
       </c>
-      <c r="B432" s="4" t="s">
+      <c r="B432" s="3" t="s">
         <v>877</v>
       </c>
       <c r="C432">
@@ -15780,7 +15767,7 @@
       <c r="A433" t="s">
         <v>685</v>
       </c>
-      <c r="B433" s="4" t="s">
+      <c r="B433" s="3" t="s">
         <v>879</v>
       </c>
       <c r="C433">
@@ -15800,7 +15787,7 @@
       <c r="A434" t="s">
         <v>685</v>
       </c>
-      <c r="B434" s="4" t="s">
+      <c r="B434" s="3" t="s">
         <v>881</v>
       </c>
       <c r="C434">
@@ -15823,7 +15810,7 @@
       <c r="A435" t="s">
         <v>685</v>
       </c>
-      <c r="B435" s="4" t="s">
+      <c r="B435" s="3" t="s">
         <v>883</v>
       </c>
       <c r="C435">
@@ -15846,7 +15833,7 @@
       <c r="A436" t="s">
         <v>685</v>
       </c>
-      <c r="B436" s="4" t="s">
+      <c r="B436" s="3" t="s">
         <v>885</v>
       </c>
       <c r="C436">
@@ -15866,7 +15853,7 @@
       <c r="A437" t="s">
         <v>685</v>
       </c>
-      <c r="B437" s="4" t="s">
+      <c r="B437" s="3" t="s">
         <v>887</v>
       </c>
       <c r="C437">
@@ -15886,7 +15873,7 @@
       <c r="A438" t="s">
         <v>685</v>
       </c>
-      <c r="B438" s="4" t="s">
+      <c r="B438" s="3" t="s">
         <v>889</v>
       </c>
       <c r="C438">
@@ -15909,7 +15896,7 @@
       <c r="A439" t="s">
         <v>685</v>
       </c>
-      <c r="B439" s="4" t="s">
+      <c r="B439" s="3" t="s">
         <v>891</v>
       </c>
       <c r="C439">
@@ -15929,7 +15916,7 @@
       <c r="A440" t="s">
         <v>685</v>
       </c>
-      <c r="B440" s="4" t="s">
+      <c r="B440" s="3" t="s">
         <v>893</v>
       </c>
       <c r="C440">
@@ -15949,7 +15936,7 @@
       <c r="A441" t="s">
         <v>685</v>
       </c>
-      <c r="B441" s="4" t="s">
+      <c r="B441" s="3" t="s">
         <v>895</v>
       </c>
       <c r="C441">
@@ -15969,7 +15956,7 @@
       <c r="A442" t="s">
         <v>685</v>
       </c>
-      <c r="B442" s="4" t="s">
+      <c r="B442" s="3" t="s">
         <v>897</v>
       </c>
       <c r="C442">
@@ -15989,7 +15976,7 @@
       <c r="A443" t="s">
         <v>685</v>
       </c>
-      <c r="B443" s="4" t="s">
+      <c r="B443" s="3" t="s">
         <v>899</v>
       </c>
       <c r="C443">
@@ -16009,7 +15996,7 @@
       <c r="A444" t="s">
         <v>685</v>
       </c>
-      <c r="B444" s="4" t="s">
+      <c r="B444" s="3" t="s">
         <v>901</v>
       </c>
       <c r="C444">
@@ -16029,7 +16016,7 @@
       <c r="A445" t="s">
         <v>685</v>
       </c>
-      <c r="B445" s="4" t="s">
+      <c r="B445" s="3" t="s">
         <v>903</v>
       </c>
       <c r="C445">
@@ -16049,7 +16036,7 @@
       <c r="A446" t="s">
         <v>685</v>
       </c>
-      <c r="B446" s="4" t="s">
+      <c r="B446" s="3" t="s">
         <v>905</v>
       </c>
       <c r="C446">
@@ -16069,7 +16056,7 @@
       <c r="A447" t="s">
         <v>685</v>
       </c>
-      <c r="B447" s="4" t="s">
+      <c r="B447" s="3" t="s">
         <v>907</v>
       </c>
       <c r="C447">
@@ -16089,7 +16076,7 @@
       <c r="A448" t="s">
         <v>685</v>
       </c>
-      <c r="B448" s="4" t="s">
+      <c r="B448" s="3" t="s">
         <v>909</v>
       </c>
       <c r="C448">
@@ -16109,7 +16096,7 @@
       <c r="A449" t="s">
         <v>685</v>
       </c>
-      <c r="B449" s="4" t="s">
+      <c r="B449" s="3" t="s">
         <v>911</v>
       </c>
       <c r="C449">
@@ -16129,7 +16116,7 @@
       <c r="A450" t="s">
         <v>685</v>
       </c>
-      <c r="B450" s="4" t="s">
+      <c r="B450" s="3" t="s">
         <v>913</v>
       </c>
       <c r="C450">
@@ -16149,7 +16136,7 @@
       <c r="A451" t="s">
         <v>685</v>
       </c>
-      <c r="B451" s="4" t="s">
+      <c r="B451" s="3" t="s">
         <v>915</v>
       </c>
       <c r="C451">
@@ -16169,7 +16156,7 @@
       <c r="A452" t="s">
         <v>685</v>
       </c>
-      <c r="B452" s="4" t="s">
+      <c r="B452" s="3" t="s">
         <v>917</v>
       </c>
       <c r="C452">
@@ -16189,7 +16176,7 @@
       <c r="A453" t="s">
         <v>685</v>
       </c>
-      <c r="B453" s="4" t="s">
+      <c r="B453" s="3" t="s">
         <v>919</v>
       </c>
       <c r="C453">
@@ -16209,7 +16196,7 @@
       <c r="A454" t="s">
         <v>685</v>
       </c>
-      <c r="B454" s="4" t="s">
+      <c r="B454" s="3" t="s">
         <v>921</v>
       </c>
       <c r="C454">
@@ -16229,7 +16216,7 @@
       <c r="A455" t="s">
         <v>685</v>
       </c>
-      <c r="B455" s="4" t="s">
+      <c r="B455" s="3" t="s">
         <v>923</v>
       </c>
       <c r="C455">
@@ -16249,7 +16236,7 @@
       <c r="A456" t="s">
         <v>685</v>
       </c>
-      <c r="B456" s="4" t="s">
+      <c r="B456" s="3" t="s">
         <v>925</v>
       </c>
       <c r="C456">
@@ -16269,7 +16256,7 @@
       <c r="A457" t="s">
         <v>685</v>
       </c>
-      <c r="B457" s="4" t="s">
+      <c r="B457" s="3" t="s">
         <v>927</v>
       </c>
       <c r="C457">
@@ -16289,7 +16276,7 @@
       <c r="A458" t="s">
         <v>685</v>
       </c>
-      <c r="B458" s="4" t="s">
+      <c r="B458" s="3" t="s">
         <v>929</v>
       </c>
       <c r="C458">
@@ -16309,7 +16296,7 @@
       <c r="A459" t="s">
         <v>685</v>
       </c>
-      <c r="B459" s="4" t="s">
+      <c r="B459" s="3" t="s">
         <v>931</v>
       </c>
       <c r="C459">
@@ -16332,7 +16319,7 @@
       <c r="A460" t="s">
         <v>685</v>
       </c>
-      <c r="B460" s="4" t="s">
+      <c r="B460" s="3" t="s">
         <v>933</v>
       </c>
       <c r="C460">
@@ -16355,7 +16342,7 @@
       <c r="A461" t="s">
         <v>685</v>
       </c>
-      <c r="B461" s="4" t="s">
+      <c r="B461" s="3" t="s">
         <v>935</v>
       </c>
       <c r="C461">
@@ -16375,7 +16362,7 @@
       <c r="A462" t="s">
         <v>685</v>
       </c>
-      <c r="B462" s="4" t="s">
+      <c r="B462" s="3" t="s">
         <v>937</v>
       </c>
       <c r="C462">
@@ -16395,7 +16382,7 @@
       <c r="A463" t="s">
         <v>685</v>
       </c>
-      <c r="B463" s="4" t="s">
+      <c r="B463" s="3" t="s">
         <v>939</v>
       </c>
       <c r="C463">
@@ -16415,7 +16402,7 @@
       <c r="A464" t="s">
         <v>685</v>
       </c>
-      <c r="B464" s="4" t="s">
+      <c r="B464" s="3" t="s">
         <v>941</v>
       </c>
       <c r="C464">
@@ -16435,7 +16422,7 @@
       <c r="A465" t="s">
         <v>685</v>
       </c>
-      <c r="B465" s="4" t="s">
+      <c r="B465" s="3" t="s">
         <v>943</v>
       </c>
       <c r="C465">
@@ -16458,7 +16445,7 @@
       <c r="A466" t="s">
         <v>685</v>
       </c>
-      <c r="B466" s="4" t="s">
+      <c r="B466" s="3" t="s">
         <v>945</v>
       </c>
       <c r="C466">
@@ -16478,7 +16465,7 @@
       <c r="A467" t="s">
         <v>685</v>
       </c>
-      <c r="B467" s="4" t="s">
+      <c r="B467" s="3" t="s">
         <v>947</v>
       </c>
       <c r="C467">
@@ -16498,7 +16485,7 @@
       <c r="A468" t="s">
         <v>685</v>
       </c>
-      <c r="B468" s="4" t="s">
+      <c r="B468" s="3" t="s">
         <v>949</v>
       </c>
       <c r="C468">
@@ -16518,7 +16505,7 @@
       <c r="A469" t="s">
         <v>685</v>
       </c>
-      <c r="B469" s="4" t="s">
+      <c r="B469" s="3" t="s">
         <v>951</v>
       </c>
       <c r="C469">
@@ -16541,7 +16528,7 @@
       <c r="A470" t="s">
         <v>685</v>
       </c>
-      <c r="B470" s="4" t="s">
+      <c r="B470" s="3" t="s">
         <v>953</v>
       </c>
       <c r="C470">
@@ -16561,7 +16548,7 @@
       <c r="A471" t="s">
         <v>685</v>
       </c>
-      <c r="B471" s="4" t="s">
+      <c r="B471" s="3" t="s">
         <v>955</v>
       </c>
       <c r="C471">
@@ -16581,7 +16568,7 @@
       <c r="A472" t="s">
         <v>685</v>
       </c>
-      <c r="B472" s="4" t="s">
+      <c r="B472" s="3" t="s">
         <v>957</v>
       </c>
       <c r="C472">
@@ -16601,7 +16588,7 @@
       <c r="A473" t="s">
         <v>685</v>
       </c>
-      <c r="B473" s="4" t="s">
+      <c r="B473" s="3" t="s">
         <v>959</v>
       </c>
       <c r="C473">
@@ -16621,7 +16608,7 @@
       <c r="A474" t="s">
         <v>685</v>
       </c>
-      <c r="B474" s="4" t="s">
+      <c r="B474" s="3" t="s">
         <v>961</v>
       </c>
       <c r="C474">
@@ -16641,7 +16628,7 @@
       <c r="A475" t="s">
         <v>685</v>
       </c>
-      <c r="B475" s="4" t="s">
+      <c r="B475" s="3" t="s">
         <v>963</v>
       </c>
       <c r="C475">
@@ -16661,7 +16648,7 @@
       <c r="A476" t="s">
         <v>685</v>
       </c>
-      <c r="B476" s="4" t="s">
+      <c r="B476" s="3" t="s">
         <v>965</v>
       </c>
       <c r="C476">
@@ -16684,7 +16671,7 @@
       <c r="A477" t="s">
         <v>685</v>
       </c>
-      <c r="B477" s="4" t="s">
+      <c r="B477" s="3" t="s">
         <v>967</v>
       </c>
       <c r="C477">
@@ -16704,7 +16691,7 @@
       <c r="A478" t="s">
         <v>685</v>
       </c>
-      <c r="B478" s="4" t="s">
+      <c r="B478" s="3" t="s">
         <v>969</v>
       </c>
       <c r="C478">
@@ -16727,7 +16714,7 @@
       <c r="A479" t="s">
         <v>685</v>
       </c>
-      <c r="B479" s="4" t="s">
+      <c r="B479" s="3" t="s">
         <v>971</v>
       </c>
       <c r="C479">
@@ -16750,7 +16737,7 @@
       <c r="A480" t="s">
         <v>685</v>
       </c>
-      <c r="B480" s="4" t="s">
+      <c r="B480" s="3" t="s">
         <v>973</v>
       </c>
       <c r="C480">
@@ -16770,7 +16757,7 @@
       <c r="A481" t="s">
         <v>685</v>
       </c>
-      <c r="B481" s="4" t="s">
+      <c r="B481" s="3" t="s">
         <v>975</v>
       </c>
       <c r="C481">
@@ -16790,7 +16777,7 @@
       <c r="A482" t="s">
         <v>685</v>
       </c>
-      <c r="B482" s="4" t="s">
+      <c r="B482" s="3" t="s">
         <v>977</v>
       </c>
       <c r="C482">
@@ -16810,7 +16797,7 @@
       <c r="A483" t="s">
         <v>685</v>
       </c>
-      <c r="B483" s="4" t="s">
+      <c r="B483" s="3" t="s">
         <v>979</v>
       </c>
       <c r="C483">
@@ -16830,7 +16817,7 @@
       <c r="A484" t="s">
         <v>685</v>
       </c>
-      <c r="B484" s="4" t="s">
+      <c r="B484" s="3" t="s">
         <v>981</v>
       </c>
       <c r="C484">
@@ -16853,7 +16840,7 @@
       <c r="A485" t="s">
         <v>685</v>
       </c>
-      <c r="B485" s="4" t="s">
+      <c r="B485" s="3" t="s">
         <v>983</v>
       </c>
       <c r="C485">
@@ -16873,7 +16860,7 @@
       <c r="A486" t="s">
         <v>685</v>
       </c>
-      <c r="B486" s="4" t="s">
+      <c r="B486" s="3" t="s">
         <v>985</v>
       </c>
       <c r="C486">
@@ -16896,7 +16883,7 @@
       <c r="A487" t="s">
         <v>685</v>
       </c>
-      <c r="B487" s="4" t="s">
+      <c r="B487" s="3" t="s">
         <v>987</v>
       </c>
       <c r="C487">
@@ -16916,7 +16903,7 @@
       <c r="A488" t="s">
         <v>685</v>
       </c>
-      <c r="B488" s="4" t="s">
+      <c r="B488" s="3" t="s">
         <v>989</v>
       </c>
       <c r="C488">
@@ -16936,7 +16923,7 @@
       <c r="A489" t="s">
         <v>685</v>
       </c>
-      <c r="B489" s="4" t="s">
+      <c r="B489" s="3" t="s">
         <v>991</v>
       </c>
       <c r="C489">
@@ -16956,7 +16943,7 @@
       <c r="A490" t="s">
         <v>685</v>
       </c>
-      <c r="B490" s="4" t="s">
+      <c r="B490" s="3" t="s">
         <v>993</v>
       </c>
       <c r="C490">
@@ -16976,7 +16963,7 @@
       <c r="A491" t="s">
         <v>685</v>
       </c>
-      <c r="B491" s="4" t="s">
+      <c r="B491" s="3" t="s">
         <v>995</v>
       </c>
       <c r="C491">
@@ -16996,7 +16983,7 @@
       <c r="A492" t="s">
         <v>685</v>
       </c>
-      <c r="B492" s="4" t="s">
+      <c r="B492" s="3" t="s">
         <v>997</v>
       </c>
       <c r="C492">
@@ -17019,7 +17006,7 @@
       <c r="A493" t="s">
         <v>685</v>
       </c>
-      <c r="B493" s="4" t="s">
+      <c r="B493" s="3" t="s">
         <v>999</v>
       </c>
       <c r="C493">
@@ -17039,7 +17026,7 @@
       <c r="A494" t="s">
         <v>685</v>
       </c>
-      <c r="B494" s="4" t="s">
+      <c r="B494" s="3" t="s">
         <v>1001</v>
       </c>
       <c r="C494">
@@ -17059,7 +17046,7 @@
       <c r="A495" t="s">
         <v>685</v>
       </c>
-      <c r="B495" s="4" t="s">
+      <c r="B495" s="3" t="s">
         <v>1003</v>
       </c>
       <c r="C495">
@@ -17079,7 +17066,7 @@
       <c r="A496" t="s">
         <v>685</v>
       </c>
-      <c r="B496" s="4" t="s">
+      <c r="B496" s="3" t="s">
         <v>1005</v>
       </c>
       <c r="C496">
@@ -17102,7 +17089,7 @@
       <c r="A497" t="s">
         <v>685</v>
       </c>
-      <c r="B497" s="4" t="s">
+      <c r="B497" s="3" t="s">
         <v>1007</v>
       </c>
       <c r="C497">
@@ -17125,7 +17112,7 @@
       <c r="A498" t="s">
         <v>685</v>
       </c>
-      <c r="B498" s="4" t="s">
+      <c r="B498" s="3" t="s">
         <v>1009</v>
       </c>
       <c r="C498">
@@ -17145,7 +17132,7 @@
       <c r="A499" t="s">
         <v>685</v>
       </c>
-      <c r="B499" s="4" t="s">
+      <c r="B499" s="3" t="s">
         <v>1011</v>
       </c>
       <c r="C499">
@@ -17165,7 +17152,7 @@
       <c r="A500" t="s">
         <v>685</v>
       </c>
-      <c r="B500" s="4" t="s">
+      <c r="B500" s="3" t="s">
         <v>1013</v>
       </c>
       <c r="C500">
@@ -17185,7 +17172,7 @@
       <c r="A501" t="s">
         <v>685</v>
       </c>
-      <c r="B501" s="4" t="s">
+      <c r="B501" s="3" t="s">
         <v>1015</v>
       </c>
       <c r="C501">
@@ -17208,7 +17195,7 @@
       <c r="A502" t="s">
         <v>685</v>
       </c>
-      <c r="B502" s="4" t="s">
+      <c r="B502" s="3" t="s">
         <v>1017</v>
       </c>
       <c r="C502">
@@ -17228,7 +17215,7 @@
       <c r="A503" t="s">
         <v>685</v>
       </c>
-      <c r="B503" s="4" t="s">
+      <c r="B503" s="3" t="s">
         <v>1019</v>
       </c>
       <c r="C503">
@@ -17248,7 +17235,7 @@
       <c r="A504" t="s">
         <v>685</v>
       </c>
-      <c r="B504" s="4" t="s">
+      <c r="B504" s="3" t="s">
         <v>1021</v>
       </c>
       <c r="C504">
@@ -17268,7 +17255,7 @@
       <c r="A505" t="s">
         <v>685</v>
       </c>
-      <c r="B505" s="4" t="s">
+      <c r="B505" s="3" t="s">
         <v>1023</v>
       </c>
       <c r="C505">
@@ -17291,7 +17278,7 @@
       <c r="A506" t="s">
         <v>685</v>
       </c>
-      <c r="B506" s="4" t="s">
+      <c r="B506" s="3" t="s">
         <v>1025</v>
       </c>
       <c r="C506">
@@ -17311,7 +17298,7 @@
       <c r="A507" t="s">
         <v>685</v>
       </c>
-      <c r="B507" s="4" t="s">
+      <c r="B507" s="3" t="s">
         <v>1027</v>
       </c>
       <c r="C507">
@@ -17331,7 +17318,7 @@
       <c r="A508" t="s">
         <v>685</v>
       </c>
-      <c r="B508" s="4" t="s">
+      <c r="B508" s="3" t="s">
         <v>1029</v>
       </c>
       <c r="C508">
@@ -17351,7 +17338,7 @@
       <c r="A509" t="s">
         <v>685</v>
       </c>
-      <c r="B509" s="4" t="s">
+      <c r="B509" s="3" t="s">
         <v>1031</v>
       </c>
       <c r="C509">
@@ -17371,7 +17358,7 @@
       <c r="A510" t="s">
         <v>685</v>
       </c>
-      <c r="B510" s="4" t="s">
+      <c r="B510" s="3" t="s">
         <v>1033</v>
       </c>
       <c r="C510">
@@ -17391,7 +17378,7 @@
       <c r="A511" t="s">
         <v>685</v>
       </c>
-      <c r="B511" s="4" t="s">
+      <c r="B511" s="3" t="s">
         <v>1035</v>
       </c>
       <c r="C511">
@@ -17411,7 +17398,7 @@
       <c r="A512" t="s">
         <v>685</v>
       </c>
-      <c r="B512" s="4" t="s">
+      <c r="B512" s="3" t="s">
         <v>1037</v>
       </c>
       <c r="C512">
@@ -17431,7 +17418,7 @@
       <c r="A513" t="s">
         <v>685</v>
       </c>
-      <c r="B513" s="4" t="s">
+      <c r="B513" s="3" t="s">
         <v>1039</v>
       </c>
       <c r="C513">
@@ -17451,7 +17438,7 @@
       <c r="A514" t="s">
         <v>685</v>
       </c>
-      <c r="B514" s="4" t="s">
+      <c r="B514" s="3" t="s">
         <v>1041</v>
       </c>
       <c r="C514">
@@ -17471,7 +17458,7 @@
       <c r="A515" t="s">
         <v>685</v>
       </c>
-      <c r="B515" s="4" t="s">
+      <c r="B515" s="3" t="s">
         <v>1043</v>
       </c>
       <c r="C515">
@@ -17491,7 +17478,7 @@
       <c r="A516" t="s">
         <v>685</v>
       </c>
-      <c r="B516" s="4" t="s">
+      <c r="B516" s="3" t="s">
         <v>1045</v>
       </c>
       <c r="C516">
@@ -17511,7 +17498,7 @@
       <c r="A517" t="s">
         <v>685</v>
       </c>
-      <c r="B517" s="4" t="s">
+      <c r="B517" s="3" t="s">
         <v>1047</v>
       </c>
       <c r="C517">
@@ -17531,7 +17518,7 @@
       <c r="A518" t="s">
         <v>685</v>
       </c>
-      <c r="B518" s="4" t="s">
+      <c r="B518" s="3" t="s">
         <v>1049</v>
       </c>
       <c r="C518">
@@ -17551,7 +17538,7 @@
       <c r="A519" t="s">
         <v>685</v>
       </c>
-      <c r="B519" s="4" t="s">
+      <c r="B519" s="3" t="s">
         <v>1051</v>
       </c>
       <c r="C519">
@@ -17574,7 +17561,7 @@
       <c r="A520" t="s">
         <v>685</v>
       </c>
-      <c r="B520" s="4" t="s">
+      <c r="B520" s="3" t="s">
         <v>1053</v>
       </c>
       <c r="C520">
@@ -17594,7 +17581,7 @@
       <c r="A521" t="s">
         <v>685</v>
       </c>
-      <c r="B521" s="4" t="s">
+      <c r="B521" s="3" t="s">
         <v>1055</v>
       </c>
       <c r="C521">
@@ -17614,7 +17601,7 @@
       <c r="A522" t="s">
         <v>685</v>
       </c>
-      <c r="B522" s="4" t="s">
+      <c r="B522" s="3" t="s">
         <v>1057</v>
       </c>
       <c r="C522">
@@ -17634,7 +17621,7 @@
       <c r="A523" t="s">
         <v>685</v>
       </c>
-      <c r="B523" s="4" t="s">
+      <c r="B523" s="3" t="s">
         <v>1059</v>
       </c>
       <c r="C523">
@@ -17654,7 +17641,7 @@
       <c r="A524" t="s">
         <v>685</v>
       </c>
-      <c r="B524" s="4" t="s">
+      <c r="B524" s="3" t="s">
         <v>1061</v>
       </c>
       <c r="C524">
@@ -17674,7 +17661,7 @@
       <c r="A525" t="s">
         <v>685</v>
       </c>
-      <c r="B525" s="4" t="s">
+      <c r="B525" s="3" t="s">
         <v>1063</v>
       </c>
       <c r="C525">
@@ -17694,7 +17681,7 @@
       <c r="A526" t="s">
         <v>685</v>
       </c>
-      <c r="B526" s="4" t="s">
+      <c r="B526" s="3" t="s">
         <v>1065</v>
       </c>
       <c r="C526">
@@ -17714,7 +17701,7 @@
       <c r="A527" t="s">
         <v>685</v>
       </c>
-      <c r="B527" s="4" t="s">
+      <c r="B527" s="3" t="s">
         <v>1067</v>
       </c>
       <c r="C527">
@@ -17737,7 +17724,7 @@
       <c r="A528" t="s">
         <v>685</v>
       </c>
-      <c r="B528" s="4" t="s">
+      <c r="B528" s="3" t="s">
         <v>1069</v>
       </c>
       <c r="C528">
@@ -17757,7 +17744,7 @@
       <c r="A529" t="s">
         <v>685</v>
       </c>
-      <c r="B529" s="4" t="s">
+      <c r="B529" s="3" t="s">
         <v>1071</v>
       </c>
       <c r="C529">
@@ -17780,7 +17767,7 @@
       <c r="A530" t="s">
         <v>685</v>
       </c>
-      <c r="B530" s="4" t="s">
+      <c r="B530" s="3" t="s">
         <v>1073</v>
       </c>
       <c r="C530">
@@ -17800,7 +17787,7 @@
       <c r="A531" t="s">
         <v>685</v>
       </c>
-      <c r="B531" s="4" t="s">
+      <c r="B531" s="3" t="s">
         <v>1075</v>
       </c>
       <c r="C531">
@@ -17820,7 +17807,7 @@
       <c r="A532" t="s">
         <v>685</v>
       </c>
-      <c r="B532" s="4" t="s">
+      <c r="B532" s="3" t="s">
         <v>1077</v>
       </c>
       <c r="C532">
@@ -17840,7 +17827,7 @@
       <c r="A533" t="s">
         <v>685</v>
       </c>
-      <c r="B533" s="4" t="s">
+      <c r="B533" s="3" t="s">
         <v>1079</v>
       </c>
       <c r="C533">
@@ -17860,7 +17847,7 @@
       <c r="A534" t="s">
         <v>685</v>
       </c>
-      <c r="B534" s="4" t="s">
+      <c r="B534" s="3" t="s">
         <v>1081</v>
       </c>
       <c r="C534">
@@ -17880,7 +17867,7 @@
       <c r="A535" t="s">
         <v>685</v>
       </c>
-      <c r="B535" s="4" t="s">
+      <c r="B535" s="3" t="s">
         <v>1083</v>
       </c>
       <c r="C535">
@@ -17900,7 +17887,7 @@
       <c r="A536" t="s">
         <v>685</v>
       </c>
-      <c r="B536" s="4" t="s">
+      <c r="B536" s="3" t="s">
         <v>1085</v>
       </c>
       <c r="C536">
@@ -17920,7 +17907,7 @@
       <c r="A537" t="s">
         <v>685</v>
       </c>
-      <c r="B537" s="4" t="s">
+      <c r="B537" s="3" t="s">
         <v>1087</v>
       </c>
       <c r="C537">
@@ -17943,7 +17930,7 @@
       <c r="A538" t="s">
         <v>685</v>
       </c>
-      <c r="B538" s="4" t="s">
+      <c r="B538" s="3" t="s">
         <v>1089</v>
       </c>
       <c r="C538">
@@ -17963,7 +17950,7 @@
       <c r="A539" t="s">
         <v>685</v>
       </c>
-      <c r="B539" s="4" t="s">
+      <c r="B539" s="3" t="s">
         <v>1091</v>
       </c>
       <c r="C539">
@@ -17983,7 +17970,7 @@
       <c r="A540" t="s">
         <v>685</v>
       </c>
-      <c r="B540" s="4" t="s">
+      <c r="B540" s="3" t="s">
         <v>1093</v>
       </c>
       <c r="C540">
@@ -18003,7 +17990,7 @@
       <c r="A541" t="s">
         <v>685</v>
       </c>
-      <c r="B541" s="4" t="s">
+      <c r="B541" s="3" t="s">
         <v>1095</v>
       </c>
       <c r="C541">
@@ -18023,7 +18010,7 @@
       <c r="A542" t="s">
         <v>685</v>
       </c>
-      <c r="B542" s="4" t="s">
+      <c r="B542" s="3" t="s">
         <v>1097</v>
       </c>
       <c r="C542">
@@ -18043,7 +18030,7 @@
       <c r="A543" t="s">
         <v>685</v>
       </c>
-      <c r="B543" s="4" t="s">
+      <c r="B543" s="3" t="s">
         <v>1099</v>
       </c>
       <c r="C543">
@@ -18066,7 +18053,7 @@
       <c r="A544" t="s">
         <v>685</v>
       </c>
-      <c r="B544" s="4" t="s">
+      <c r="B544" s="3" t="s">
         <v>1101</v>
       </c>
       <c r="C544">
@@ -18089,7 +18076,7 @@
       <c r="A545" t="s">
         <v>685</v>
       </c>
-      <c r="B545" s="4" t="s">
+      <c r="B545" s="3" t="s">
         <v>1103</v>
       </c>
       <c r="C545">
@@ -18112,7 +18099,7 @@
       <c r="A546" t="s">
         <v>685</v>
       </c>
-      <c r="B546" s="4" t="s">
+      <c r="B546" s="3" t="s">
         <v>1105</v>
       </c>
       <c r="C546">
@@ -18132,7 +18119,7 @@
       <c r="A547" t="s">
         <v>685</v>
       </c>
-      <c r="B547" s="4" t="s">
+      <c r="B547" s="3" t="s">
         <v>1107</v>
       </c>
       <c r="C547">
@@ -18155,7 +18142,7 @@
       <c r="A548" t="s">
         <v>685</v>
       </c>
-      <c r="B548" s="4" t="s">
+      <c r="B548" s="3" t="s">
         <v>1109</v>
       </c>
       <c r="C548">
@@ -18175,7 +18162,7 @@
       <c r="A549" t="s">
         <v>685</v>
       </c>
-      <c r="B549" s="4" t="s">
+      <c r="B549" s="3" t="s">
         <v>1111</v>
       </c>
       <c r="C549">
@@ -18195,7 +18182,7 @@
       <c r="A550" t="s">
         <v>685</v>
       </c>
-      <c r="B550" s="4" t="s">
+      <c r="B550" s="3" t="s">
         <v>1113</v>
       </c>
       <c r="C550">
@@ -18215,7 +18202,7 @@
       <c r="A551" t="s">
         <v>685</v>
       </c>
-      <c r="B551" s="4" t="s">
+      <c r="B551" s="3" t="s">
         <v>1115</v>
       </c>
       <c r="C551">
@@ -18235,7 +18222,7 @@
       <c r="A552" t="s">
         <v>685</v>
       </c>
-      <c r="B552" s="4" t="s">
+      <c r="B552" s="3" t="s">
         <v>1117</v>
       </c>
       <c r="C552">
@@ -18255,7 +18242,7 @@
       <c r="A553" t="s">
         <v>685</v>
       </c>
-      <c r="B553" s="4" t="s">
+      <c r="B553" s="3" t="s">
         <v>1119</v>
       </c>
       <c r="C553">
@@ -18275,7 +18262,7 @@
       <c r="A554" t="s">
         <v>685</v>
       </c>
-      <c r="B554" s="4" t="s">
+      <c r="B554" s="3" t="s">
         <v>1121</v>
       </c>
       <c r="C554">
@@ -18295,7 +18282,7 @@
       <c r="A555" t="s">
         <v>685</v>
       </c>
-      <c r="B555" s="4" t="s">
+      <c r="B555" s="3" t="s">
         <v>1123</v>
       </c>
       <c r="C555">
@@ -18315,7 +18302,7 @@
       <c r="A556" t="s">
         <v>685</v>
       </c>
-      <c r="B556" s="4" t="s">
+      <c r="B556" s="3" t="s">
         <v>1125</v>
       </c>
       <c r="C556">
@@ -18335,7 +18322,7 @@
       <c r="A557" t="s">
         <v>685</v>
       </c>
-      <c r="B557" s="4" t="s">
+      <c r="B557" s="3" t="s">
         <v>1127</v>
       </c>
       <c r="C557">
@@ -18355,7 +18342,7 @@
       <c r="A558" t="s">
         <v>685</v>
       </c>
-      <c r="B558" s="4" t="s">
+      <c r="B558" s="3" t="s">
         <v>1129</v>
       </c>
       <c r="C558">
@@ -18375,7 +18362,7 @@
       <c r="A559" t="s">
         <v>685</v>
       </c>
-      <c r="B559" s="4" t="s">
+      <c r="B559" s="3" t="s">
         <v>1131</v>
       </c>
       <c r="C559">
@@ -18398,7 +18385,7 @@
       <c r="A560" t="s">
         <v>685</v>
       </c>
-      <c r="B560" s="4" t="s">
+      <c r="B560" s="3" t="s">
         <v>1133</v>
       </c>
       <c r="C560">
@@ -18421,7 +18408,7 @@
       <c r="A561" t="s">
         <v>685</v>
       </c>
-      <c r="B561" s="4" t="s">
+      <c r="B561" s="3" t="s">
         <v>1135</v>
       </c>
       <c r="C561">
@@ -18444,7 +18431,7 @@
       <c r="A562" t="s">
         <v>685</v>
       </c>
-      <c r="B562" s="4" t="s">
+      <c r="B562" s="3" t="s">
         <v>1137</v>
       </c>
       <c r="C562">
@@ -18467,7 +18454,7 @@
       <c r="A563" t="s">
         <v>685</v>
       </c>
-      <c r="B563" s="4" t="s">
+      <c r="B563" s="3" t="s">
         <v>1139</v>
       </c>
       <c r="C563">
@@ -18490,7 +18477,7 @@
       <c r="A564" t="s">
         <v>685</v>
       </c>
-      <c r="B564" s="4" t="s">
+      <c r="B564" s="3" t="s">
         <v>1141</v>
       </c>
       <c r="C564">
@@ -18513,7 +18500,7 @@
       <c r="A565" t="s">
         <v>685</v>
       </c>
-      <c r="B565" s="4" t="s">
+      <c r="B565" s="3" t="s">
         <v>1143</v>
       </c>
       <c r="C565">
@@ -18536,7 +18523,7 @@
       <c r="A566" t="s">
         <v>685</v>
       </c>
-      <c r="B566" s="4" t="s">
+      <c r="B566" s="3" t="s">
         <v>1145</v>
       </c>
       <c r="C566">
@@ -18559,7 +18546,7 @@
       <c r="A567" t="s">
         <v>685</v>
       </c>
-      <c r="B567" s="4" t="s">
+      <c r="B567" s="3" t="s">
         <v>1147</v>
       </c>
       <c r="C567">
@@ -18582,7 +18569,7 @@
       <c r="A568" t="s">
         <v>685</v>
       </c>
-      <c r="B568" s="4" t="s">
+      <c r="B568" s="3" t="s">
         <v>1149</v>
       </c>
       <c r="C568">
@@ -18605,7 +18592,7 @@
       <c r="A569" t="s">
         <v>685</v>
       </c>
-      <c r="B569" s="4" t="s">
+      <c r="B569" s="3" t="s">
         <v>1151</v>
       </c>
       <c r="C569">
@@ -18628,7 +18615,7 @@
       <c r="A570" t="s">
         <v>685</v>
       </c>
-      <c r="B570" s="4" t="s">
+      <c r="B570" s="3" t="s">
         <v>1153</v>
       </c>
       <c r="C570">
@@ -18651,7 +18638,7 @@
       <c r="A571" t="s">
         <v>685</v>
       </c>
-      <c r="B571" s="4" t="s">
+      <c r="B571" s="3" t="s">
         <v>1155</v>
       </c>
       <c r="C571">
@@ -18674,7 +18661,7 @@
       <c r="A572" t="s">
         <v>685</v>
       </c>
-      <c r="B572" s="4" t="s">
+      <c r="B572" s="3" t="s">
         <v>1157</v>
       </c>
       <c r="C572">
@@ -18697,7 +18684,7 @@
       <c r="A573" t="s">
         <v>685</v>
       </c>
-      <c r="B573" s="4" t="s">
+      <c r="B573" s="3" t="s">
         <v>1159</v>
       </c>
       <c r="C573">
@@ -18720,7 +18707,7 @@
       <c r="A574" t="s">
         <v>685</v>
       </c>
-      <c r="B574" s="4" t="s">
+      <c r="B574" s="3" t="s">
         <v>1161</v>
       </c>
       <c r="C574">
@@ -18743,7 +18730,7 @@
       <c r="A575" t="s">
         <v>685</v>
       </c>
-      <c r="B575" s="4" t="s">
+      <c r="B575" s="3" t="s">
         <v>1163</v>
       </c>
       <c r="C575">
@@ -18766,7 +18753,7 @@
       <c r="A576" t="s">
         <v>685</v>
       </c>
-      <c r="B576" s="4" t="s">
+      <c r="B576" s="3" t="s">
         <v>1165</v>
       </c>
       <c r="C576">
@@ -18789,7 +18776,7 @@
       <c r="A577" t="s">
         <v>685</v>
       </c>
-      <c r="B577" s="4" t="s">
+      <c r="B577" s="3" t="s">
         <v>1167</v>
       </c>
       <c r="C577">
@@ -18812,7 +18799,7 @@
       <c r="A578" t="s">
         <v>685</v>
       </c>
-      <c r="B578" s="4" t="s">
+      <c r="B578" s="3" t="s">
         <v>1169</v>
       </c>
       <c r="C578">
@@ -18835,7 +18822,7 @@
       <c r="A579" t="s">
         <v>685</v>
       </c>
-      <c r="B579" s="4" t="s">
+      <c r="B579" s="3" t="s">
         <v>1171</v>
       </c>
       <c r="C579">
@@ -18858,7 +18845,7 @@
       <c r="A580" t="s">
         <v>685</v>
       </c>
-      <c r="B580" s="4" t="s">
+      <c r="B580" s="3" t="s">
         <v>1173</v>
       </c>
       <c r="C580">
@@ -18881,7 +18868,7 @@
       <c r="A581" t="s">
         <v>685</v>
       </c>
-      <c r="B581" s="4" t="s">
+      <c r="B581" s="3" t="s">
         <v>1175</v>
       </c>
       <c r="C581">
@@ -18901,7 +18888,7 @@
       <c r="A582" t="s">
         <v>685</v>
       </c>
-      <c r="B582" s="4" t="s">
+      <c r="B582" s="3" t="s">
         <v>1177</v>
       </c>
       <c r="C582">
@@ -18924,7 +18911,7 @@
       <c r="A583" t="s">
         <v>685</v>
       </c>
-      <c r="B583" s="4" t="s">
+      <c r="B583" s="3" t="s">
         <v>1179</v>
       </c>
       <c r="C583">
@@ -18947,7 +18934,7 @@
       <c r="A584" t="s">
         <v>685</v>
       </c>
-      <c r="B584" s="4" t="s">
+      <c r="B584" s="3" t="s">
         <v>1181</v>
       </c>
       <c r="C584">
@@ -18970,7 +18957,7 @@
       <c r="A585" t="s">
         <v>685</v>
       </c>
-      <c r="B585" s="4" t="s">
+      <c r="B585" s="3" t="s">
         <v>1183</v>
       </c>
       <c r="C585">
@@ -18990,7 +18977,7 @@
       <c r="A586" t="s">
         <v>685</v>
       </c>
-      <c r="B586" s="4" t="s">
+      <c r="B586" s="3" t="s">
         <v>1185</v>
       </c>
       <c r="C586">
@@ -19010,7 +18997,7 @@
       <c r="A587" t="s">
         <v>685</v>
       </c>
-      <c r="B587" s="4" t="s">
+      <c r="B587" s="3" t="s">
         <v>1187</v>
       </c>
       <c r="C587">
@@ -19030,7 +19017,7 @@
       <c r="A588" t="s">
         <v>685</v>
       </c>
-      <c r="B588" s="4" t="s">
+      <c r="B588" s="3" t="s">
         <v>1189</v>
       </c>
       <c r="C588">
@@ -19050,7 +19037,7 @@
       <c r="A589" t="s">
         <v>685</v>
       </c>
-      <c r="B589" s="4" t="s">
+      <c r="B589" s="3" t="s">
         <v>1191</v>
       </c>
       <c r="C589">
@@ -19070,7 +19057,7 @@
       <c r="A590" t="s">
         <v>685</v>
       </c>
-      <c r="B590" s="4" t="s">
+      <c r="B590" s="3" t="s">
         <v>1193</v>
       </c>
       <c r="C590">
@@ -19090,7 +19077,7 @@
       <c r="A591" t="s">
         <v>685</v>
       </c>
-      <c r="B591" s="4" t="s">
+      <c r="B591" s="3" t="s">
         <v>1195</v>
       </c>
       <c r="C591">
@@ -19113,7 +19100,7 @@
       <c r="A592" t="s">
         <v>685</v>
       </c>
-      <c r="B592" s="4" t="s">
+      <c r="B592" s="3" t="s">
         <v>1197</v>
       </c>
       <c r="C592">
@@ -19133,7 +19120,7 @@
       <c r="A593" t="s">
         <v>685</v>
       </c>
-      <c r="B593" s="4" t="s">
+      <c r="B593" s="3" t="s">
         <v>1199</v>
       </c>
       <c r="C593">
@@ -19153,7 +19140,7 @@
       <c r="A594" t="s">
         <v>685</v>
       </c>
-      <c r="B594" s="4" t="s">
+      <c r="B594" s="3" t="s">
         <v>1201</v>
       </c>
       <c r="C594">
@@ -19173,7 +19160,7 @@
       <c r="A595" t="s">
         <v>685</v>
       </c>
-      <c r="B595" s="4" t="s">
+      <c r="B595" s="3" t="s">
         <v>1203</v>
       </c>
       <c r="C595">
@@ -19193,7 +19180,7 @@
       <c r="A596" t="s">
         <v>685</v>
       </c>
-      <c r="B596" s="4" t="s">
+      <c r="B596" s="3" t="s">
         <v>1205</v>
       </c>
       <c r="C596">
@@ -19213,7 +19200,7 @@
       <c r="A597" t="s">
         <v>685</v>
       </c>
-      <c r="B597" s="4" t="s">
+      <c r="B597" s="3" t="s">
         <v>1207</v>
       </c>
       <c r="C597">
@@ -19233,7 +19220,7 @@
       <c r="A598" t="s">
         <v>685</v>
       </c>
-      <c r="B598" s="4" t="s">
+      <c r="B598" s="3" t="s">
         <v>1209</v>
       </c>
       <c r="C598">
@@ -19256,7 +19243,7 @@
       <c r="A599" t="s">
         <v>685</v>
       </c>
-      <c r="B599" s="4" t="s">
+      <c r="B599" s="3" t="s">
         <v>1211</v>
       </c>
       <c r="C599">
@@ -19279,7 +19266,7 @@
       <c r="A600" t="s">
         <v>685</v>
       </c>
-      <c r="B600" s="4" t="s">
+      <c r="B600" s="3" t="s">
         <v>1213</v>
       </c>
       <c r="C600">
@@ -19302,7 +19289,7 @@
       <c r="A601" t="s">
         <v>685</v>
       </c>
-      <c r="B601" s="4" t="s">
+      <c r="B601" s="3" t="s">
         <v>1215</v>
       </c>
       <c r="C601">
@@ -19325,7 +19312,7 @@
       <c r="A602" t="s">
         <v>685</v>
       </c>
-      <c r="B602" s="4" t="s">
+      <c r="B602" s="3" t="s">
         <v>1217</v>
       </c>
       <c r="C602">
@@ -19348,7 +19335,7 @@
       <c r="A603" t="s">
         <v>685</v>
       </c>
-      <c r="B603" s="4" t="s">
+      <c r="B603" s="3" t="s">
         <v>1219</v>
       </c>
       <c r="C603">
@@ -19368,7 +19355,7 @@
       <c r="A604" t="s">
         <v>685</v>
       </c>
-      <c r="B604" s="4" t="s">
+      <c r="B604" s="3" t="s">
         <v>1221</v>
       </c>
       <c r="C604">
@@ -19551,7 +19538,7 @@
       <c r="A613" t="s">
         <v>685</v>
       </c>
-      <c r="B613" s="4" t="s">
+      <c r="B613" s="3" t="s">
         <v>1239</v>
       </c>
       <c r="C613">
@@ -19571,7 +19558,7 @@
       <c r="A614" t="s">
         <v>685</v>
       </c>
-      <c r="B614" s="4" t="s">
+      <c r="B614" s="3" t="s">
         <v>1241</v>
       </c>
       <c r="C614">
@@ -19591,7 +19578,7 @@
       <c r="A615" t="s">
         <v>685</v>
       </c>
-      <c r="B615" s="4" t="s">
+      <c r="B615" s="3" t="s">
         <v>1243</v>
       </c>
       <c r="C615">
@@ -19614,7 +19601,7 @@
       <c r="A616" t="s">
         <v>685</v>
       </c>
-      <c r="B616" s="4" t="s">
+      <c r="B616" s="3" t="s">
         <v>1245</v>
       </c>
       <c r="C616">
@@ -19637,7 +19624,7 @@
       <c r="A617" t="s">
         <v>685</v>
       </c>
-      <c r="B617" s="4" t="s">
+      <c r="B617" s="3" t="s">
         <v>1247</v>
       </c>
       <c r="C617">
@@ -19657,7 +19644,7 @@
       <c r="A618" t="s">
         <v>685</v>
       </c>
-      <c r="B618" s="4" t="s">
+      <c r="B618" s="3" t="s">
         <v>1249</v>
       </c>
       <c r="C618">
@@ -19677,7 +19664,7 @@
       <c r="A619" t="s">
         <v>685</v>
       </c>
-      <c r="B619" s="4" t="s">
+      <c r="B619" s="3" t="s">
         <v>1251</v>
       </c>
       <c r="C619">
@@ -19697,7 +19684,7 @@
       <c r="A620" t="s">
         <v>685</v>
       </c>
-      <c r="B620" s="4" t="s">
+      <c r="B620" s="3" t="s">
         <v>1253</v>
       </c>
       <c r="C620">
@@ -19717,7 +19704,7 @@
       <c r="A621" t="s">
         <v>685</v>
       </c>
-      <c r="B621" s="4" t="s">
+      <c r="B621" s="3" t="s">
         <v>1255</v>
       </c>
       <c r="C621">
@@ -19740,7 +19727,7 @@
       <c r="A622" t="s">
         <v>685</v>
       </c>
-      <c r="B622" s="4" t="s">
+      <c r="B622" s="3" t="s">
         <v>1257</v>
       </c>
       <c r="C622">
@@ -19763,7 +19750,7 @@
       <c r="A623" t="s">
         <v>685</v>
       </c>
-      <c r="B623" s="4" t="s">
+      <c r="B623" s="3" t="s">
         <v>1259</v>
       </c>
       <c r="C623">
@@ -19783,7 +19770,7 @@
       <c r="A624" t="s">
         <v>685</v>
       </c>
-      <c r="B624" s="4" t="s">
+      <c r="B624" s="3" t="s">
         <v>1261</v>
       </c>
       <c r="C624">
@@ -19803,7 +19790,7 @@
       <c r="A625" t="s">
         <v>685</v>
       </c>
-      <c r="B625" s="4" t="s">
+      <c r="B625" s="3" t="s">
         <v>1263</v>
       </c>
       <c r="C625">
@@ -19823,7 +19810,7 @@
       <c r="A626" t="s">
         <v>685</v>
       </c>
-      <c r="B626" s="4" t="s">
+      <c r="B626" s="3" t="s">
         <v>1265</v>
       </c>
       <c r="C626">
@@ -19843,7 +19830,7 @@
       <c r="A627" t="s">
         <v>685</v>
       </c>
-      <c r="B627" s="4" t="s">
+      <c r="B627" s="3" t="s">
         <v>1267</v>
       </c>
       <c r="C627">
@@ -19863,7 +19850,7 @@
       <c r="A628" t="s">
         <v>1269</v>
       </c>
-      <c r="B628" s="4" t="s">
+      <c r="B628" s="3" t="s">
         <v>1270</v>
       </c>
       <c r="C628">
@@ -19886,7 +19873,7 @@
       <c r="A629" t="s">
         <v>1269</v>
       </c>
-      <c r="B629" s="4" t="s">
+      <c r="B629" s="3" t="s">
         <v>1272</v>
       </c>
       <c r="C629">
@@ -19909,7 +19896,7 @@
       <c r="A630" t="s">
         <v>1269</v>
       </c>
-      <c r="B630" s="4" t="s">
+      <c r="B630" s="3" t="s">
         <v>1274</v>
       </c>
       <c r="C630">
@@ -19929,7 +19916,7 @@
       <c r="A631" t="s">
         <v>1269</v>
       </c>
-      <c r="B631" s="4" t="s">
+      <c r="B631" s="3" t="s">
         <v>1276</v>
       </c>
       <c r="C631">
@@ -19952,7 +19939,7 @@
       <c r="A632" t="s">
         <v>1269</v>
       </c>
-      <c r="B632" s="4" t="s">
+      <c r="B632" s="3" t="s">
         <v>1278</v>
       </c>
       <c r="C632">
@@ -19975,7 +19962,7 @@
       <c r="A633" t="s">
         <v>1269</v>
       </c>
-      <c r="B633" s="4" t="s">
+      <c r="B633" s="3" t="s">
         <v>1280</v>
       </c>
       <c r="C633">
@@ -19998,7 +19985,7 @@
       <c r="A634" t="s">
         <v>1269</v>
       </c>
-      <c r="B634" s="4" t="s">
+      <c r="B634" s="3" t="s">
         <v>1282</v>
       </c>
       <c r="C634">
@@ -20018,7 +20005,7 @@
       <c r="A635" t="s">
         <v>1269</v>
       </c>
-      <c r="B635" s="4" t="s">
+      <c r="B635" s="3" t="s">
         <v>1284</v>
       </c>
       <c r="C635">
@@ -20041,7 +20028,7 @@
       <c r="A636" t="s">
         <v>1269</v>
       </c>
-      <c r="B636" s="4" t="s">
+      <c r="B636" s="3" t="s">
         <v>1286</v>
       </c>
       <c r="C636">
@@ -20064,7 +20051,7 @@
       <c r="A637" t="s">
         <v>1269</v>
       </c>
-      <c r="B637" s="4" t="s">
+      <c r="B637" s="3" t="s">
         <v>1288</v>
       </c>
       <c r="C637">
@@ -20087,7 +20074,7 @@
       <c r="A638" t="s">
         <v>1269</v>
       </c>
-      <c r="B638" s="4" t="s">
+      <c r="B638" s="3" t="s">
         <v>1290</v>
       </c>
       <c r="C638">
@@ -20110,7 +20097,7 @@
       <c r="A639" t="s">
         <v>1269</v>
       </c>
-      <c r="B639" s="4" t="s">
+      <c r="B639" s="3" t="s">
         <v>1292</v>
       </c>
       <c r="C639">
@@ -20130,7 +20117,7 @@
       <c r="A640" t="s">
         <v>1269</v>
       </c>
-      <c r="B640" s="4" t="s">
+      <c r="B640" s="3" t="s">
         <v>1294</v>
       </c>
       <c r="C640">
@@ -20153,7 +20140,7 @@
       <c r="A641" t="s">
         <v>1269</v>
       </c>
-      <c r="B641" s="4" t="s">
+      <c r="B641" s="3" t="s">
         <v>1296</v>
       </c>
       <c r="C641">
@@ -20176,7 +20163,7 @@
       <c r="A642" t="s">
         <v>1269</v>
       </c>
-      <c r="B642" s="4" t="s">
+      <c r="B642" s="3" t="s">
         <v>1298</v>
       </c>
       <c r="C642">
@@ -20196,7 +20183,7 @@
       <c r="A643" t="s">
         <v>1269</v>
       </c>
-      <c r="B643" s="4" t="s">
+      <c r="B643" s="3" t="s">
         <v>1300</v>
       </c>
       <c r="C643">
@@ -20219,7 +20206,7 @@
       <c r="A644" t="s">
         <v>1269</v>
       </c>
-      <c r="B644" s="4" t="s">
+      <c r="B644" s="3" t="s">
         <v>1302</v>
       </c>
       <c r="C644">
@@ -20242,7 +20229,7 @@
       <c r="A645" t="s">
         <v>1269</v>
       </c>
-      <c r="B645" s="4" t="s">
+      <c r="B645" s="3" t="s">
         <v>1304</v>
       </c>
       <c r="C645">
@@ -20262,7 +20249,7 @@
       <c r="A646" t="s">
         <v>1269</v>
       </c>
-      <c r="B646" s="4" t="s">
+      <c r="B646" s="3" t="s">
         <v>1306</v>
       </c>
       <c r="C646">
@@ -20285,7 +20272,7 @@
       <c r="A647" t="s">
         <v>1269</v>
       </c>
-      <c r="B647" s="4" t="s">
+      <c r="B647" s="3" t="s">
         <v>1308</v>
       </c>
       <c r="C647">
@@ -20308,7 +20295,7 @@
       <c r="A648" t="s">
         <v>1269</v>
       </c>
-      <c r="B648" s="4" t="s">
+      <c r="B648" s="3" t="s">
         <v>1310</v>
       </c>
       <c r="C648">
@@ -20328,7 +20315,7 @@
       <c r="A649" t="s">
         <v>1269</v>
       </c>
-      <c r="B649" s="4" t="s">
+      <c r="B649" s="3" t="s">
         <v>1312</v>
       </c>
       <c r="C649">
@@ -20351,7 +20338,7 @@
       <c r="A650" t="s">
         <v>1269</v>
       </c>
-      <c r="B650" s="4" t="s">
+      <c r="B650" s="3" t="s">
         <v>1314</v>
       </c>
       <c r="C650">
@@ -20374,7 +20361,7 @@
       <c r="A651" t="s">
         <v>1269</v>
       </c>
-      <c r="B651" s="4" t="s">
+      <c r="B651" s="3" t="s">
         <v>1316</v>
       </c>
       <c r="C651">
@@ -20394,7 +20381,7 @@
       <c r="A652" t="s">
         <v>1269</v>
       </c>
-      <c r="B652" s="4" t="s">
+      <c r="B652" s="3" t="s">
         <v>1318</v>
       </c>
       <c r="C652">
@@ -20414,7 +20401,7 @@
       <c r="A653" t="s">
         <v>1269</v>
       </c>
-      <c r="B653" s="4" t="s">
+      <c r="B653" s="3" t="s">
         <v>1320</v>
       </c>
       <c r="C653">
@@ -20434,7 +20421,7 @@
       <c r="A654" t="s">
         <v>1269</v>
       </c>
-      <c r="B654" s="4" t="s">
+      <c r="B654" s="3" t="s">
         <v>1322</v>
       </c>
       <c r="C654">
@@ -20454,7 +20441,7 @@
       <c r="A655" t="s">
         <v>1269</v>
       </c>
-      <c r="B655" s="4" t="s">
+      <c r="B655" s="3" t="s">
         <v>1324</v>
       </c>
       <c r="C655">
@@ -20474,7 +20461,7 @@
       <c r="A656" t="s">
         <v>1269</v>
       </c>
-      <c r="B656" s="4" t="s">
+      <c r="B656" s="3" t="s">
         <v>1326</v>
       </c>
       <c r="C656">
@@ -20494,7 +20481,7 @@
       <c r="A657" t="s">
         <v>1269</v>
       </c>
-      <c r="B657" s="4" t="s">
+      <c r="B657" s="3" t="s">
         <v>1328</v>
       </c>
       <c r="C657">
@@ -20517,7 +20504,7 @@
       <c r="A658" t="s">
         <v>1269</v>
       </c>
-      <c r="B658" s="4" t="s">
+      <c r="B658" s="3" t="s">
         <v>1330</v>
       </c>
       <c r="C658">
@@ -20537,7 +20524,7 @@
       <c r="A659" t="s">
         <v>1269</v>
       </c>
-      <c r="B659" s="4" t="s">
+      <c r="B659" s="3" t="s">
         <v>1332</v>
       </c>
       <c r="C659">
@@ -20560,7 +20547,7 @@
       <c r="A660" t="s">
         <v>1269</v>
       </c>
-      <c r="B660" s="4" t="s">
+      <c r="B660" s="3" t="s">
         <v>1334</v>
       </c>
       <c r="C660">
@@ -20580,7 +20567,7 @@
       <c r="A661" t="s">
         <v>1269</v>
       </c>
-      <c r="B661" s="4" t="s">
+      <c r="B661" s="3" t="s">
         <v>1336</v>
       </c>
       <c r="C661">
@@ -20600,7 +20587,7 @@
       <c r="A662" t="s">
         <v>1269</v>
       </c>
-      <c r="B662" s="4" t="s">
+      <c r="B662" s="3" t="s">
         <v>1338</v>
       </c>
       <c r="C662">
@@ -20620,7 +20607,7 @@
       <c r="A663" t="s">
         <v>1269</v>
       </c>
-      <c r="B663" s="4" t="s">
+      <c r="B663" s="3" t="s">
         <v>1340</v>
       </c>
       <c r="C663">
@@ -20640,7 +20627,7 @@
       <c r="A664" t="s">
         <v>1269</v>
       </c>
-      <c r="B664" s="4" t="s">
+      <c r="B664" s="3" t="s">
         <v>1342</v>
       </c>
       <c r="C664">
@@ -20663,7 +20650,7 @@
       <c r="A665" t="s">
         <v>1269</v>
       </c>
-      <c r="B665" s="4" t="s">
+      <c r="B665" s="3" t="s">
         <v>1344</v>
       </c>
       <c r="C665">
@@ -20683,7 +20670,7 @@
       <c r="A666" t="s">
         <v>1269</v>
       </c>
-      <c r="B666" s="4" t="s">
+      <c r="B666" s="3" t="s">
         <v>1346</v>
       </c>
       <c r="C666">
@@ -20706,7 +20693,7 @@
       <c r="A667" t="s">
         <v>1269</v>
       </c>
-      <c r="B667" s="4" t="s">
+      <c r="B667" s="3" t="s">
         <v>1348</v>
       </c>
       <c r="C667">
@@ -20726,7 +20713,7 @@
       <c r="A668" t="s">
         <v>1269</v>
       </c>
-      <c r="B668" s="4" t="s">
+      <c r="B668" s="3" t="s">
         <v>1350</v>
       </c>
       <c r="C668">
@@ -20746,7 +20733,7 @@
       <c r="A669" t="s">
         <v>1269</v>
       </c>
-      <c r="B669" s="4" t="s">
+      <c r="B669" s="3" t="s">
         <v>1352</v>
       </c>
       <c r="C669">
@@ -20766,7 +20753,7 @@
       <c r="A670" t="s">
         <v>1269</v>
       </c>
-      <c r="B670" s="4" t="s">
+      <c r="B670" s="3" t="s">
         <v>1354</v>
       </c>
       <c r="C670">
@@ -20786,7 +20773,7 @@
       <c r="A671" t="s">
         <v>1269</v>
       </c>
-      <c r="B671" s="4" t="s">
+      <c r="B671" s="3" t="s">
         <v>1356</v>
       </c>
       <c r="C671">
@@ -20809,7 +20796,7 @@
       <c r="A672" t="s">
         <v>1269</v>
       </c>
-      <c r="B672" s="4" t="s">
+      <c r="B672" s="3" t="s">
         <v>1358</v>
       </c>
       <c r="C672">
@@ -20829,7 +20816,7 @@
       <c r="A673" t="s">
         <v>1269</v>
       </c>
-      <c r="B673" s="4" t="s">
+      <c r="B673" s="3" t="s">
         <v>1360</v>
       </c>
       <c r="C673">
@@ -20852,7 +20839,7 @@
       <c r="A674" t="s">
         <v>1269</v>
       </c>
-      <c r="B674" s="4" t="s">
+      <c r="B674" s="3" t="s">
         <v>1362</v>
       </c>
       <c r="C674">
@@ -20872,7 +20859,7 @@
       <c r="A675" t="s">
         <v>1269</v>
       </c>
-      <c r="B675" s="4" t="s">
+      <c r="B675" s="3" t="s">
         <v>1364</v>
       </c>
       <c r="C675">
@@ -20892,7 +20879,7 @@
       <c r="A676" t="s">
         <v>1269</v>
       </c>
-      <c r="B676" s="4" t="s">
+      <c r="B676" s="3" t="s">
         <v>1366</v>
       </c>
       <c r="C676">
@@ -20912,7 +20899,7 @@
       <c r="A677" t="s">
         <v>1269</v>
       </c>
-      <c r="B677" s="4" t="s">
+      <c r="B677" s="3" t="s">
         <v>1368</v>
       </c>
       <c r="C677">
@@ -20935,7 +20922,7 @@
       <c r="A678" t="s">
         <v>1269</v>
       </c>
-      <c r="B678" s="4" t="s">
+      <c r="B678" s="3" t="s">
         <v>1370</v>
       </c>
       <c r="C678">
@@ -20955,7 +20942,7 @@
       <c r="A679" t="s">
         <v>1269</v>
       </c>
-      <c r="B679" s="4" t="s">
+      <c r="B679" s="3" t="s">
         <v>1372</v>
       </c>
       <c r="C679">
@@ -20975,7 +20962,7 @@
       <c r="A680" t="s">
         <v>1269</v>
       </c>
-      <c r="B680" s="4" t="s">
+      <c r="B680" s="3" t="s">
         <v>1374</v>
       </c>
       <c r="C680">
@@ -20995,7 +20982,7 @@
       <c r="A681" t="s">
         <v>1269</v>
       </c>
-      <c r="B681" s="4" t="s">
+      <c r="B681" s="3" t="s">
         <v>1376</v>
       </c>
       <c r="C681">
@@ -21015,7 +21002,7 @@
       <c r="A682" t="s">
         <v>1269</v>
       </c>
-      <c r="B682" s="4" t="s">
+      <c r="B682" s="3" t="s">
         <v>1378</v>
       </c>
       <c r="C682">
@@ -21035,7 +21022,7 @@
       <c r="A683" t="s">
         <v>1269</v>
       </c>
-      <c r="B683" s="4" t="s">
+      <c r="B683" s="3" t="s">
         <v>1380</v>
       </c>
       <c r="C683">
@@ -21055,7 +21042,7 @@
       <c r="A684" t="s">
         <v>1269</v>
       </c>
-      <c r="B684" s="4" t="s">
+      <c r="B684" s="3" t="s">
         <v>1382</v>
       </c>
       <c r="C684">
@@ -21075,7 +21062,7 @@
       <c r="A685" t="s">
         <v>1269</v>
       </c>
-      <c r="B685" s="4" t="s">
+      <c r="B685" s="3" t="s">
         <v>1384</v>
       </c>
       <c r="C685">
@@ -21095,7 +21082,7 @@
       <c r="A686" t="s">
         <v>1269</v>
       </c>
-      <c r="B686" s="4" t="s">
+      <c r="B686" s="3" t="s">
         <v>1386</v>
       </c>
       <c r="C686">
@@ -21115,7 +21102,7 @@
       <c r="A687" t="s">
         <v>1269</v>
       </c>
-      <c r="B687" s="4" t="s">
+      <c r="B687" s="3" t="s">
         <v>1388</v>
       </c>
       <c r="C687">
@@ -21135,7 +21122,7 @@
       <c r="A688" t="s">
         <v>1269</v>
       </c>
-      <c r="B688" s="4" t="s">
+      <c r="B688" s="3" t="s">
         <v>1390</v>
       </c>
       <c r="C688">
@@ -21155,7 +21142,7 @@
       <c r="A689" t="s">
         <v>1269</v>
       </c>
-      <c r="B689" s="4" t="s">
+      <c r="B689" s="3" t="s">
         <v>1392</v>
       </c>
       <c r="C689">
@@ -21175,7 +21162,7 @@
       <c r="A690" t="s">
         <v>1269</v>
       </c>
-      <c r="B690" s="4" t="s">
+      <c r="B690" s="3" t="s">
         <v>1394</v>
       </c>
       <c r="C690">
@@ -21195,7 +21182,7 @@
       <c r="A691" t="s">
         <v>1269</v>
       </c>
-      <c r="B691" s="4" t="s">
+      <c r="B691" s="3" t="s">
         <v>1396</v>
       </c>
       <c r="C691">
@@ -21215,7 +21202,7 @@
       <c r="A692" t="s">
         <v>1269</v>
       </c>
-      <c r="B692" s="4" t="s">
+      <c r="B692" s="3" t="s">
         <v>1398</v>
       </c>
       <c r="C692">
@@ -21235,7 +21222,7 @@
       <c r="A693" t="s">
         <v>1269</v>
       </c>
-      <c r="B693" s="4" t="s">
+      <c r="B693" s="3" t="s">
         <v>1400</v>
       </c>
       <c r="C693">
@@ -21255,7 +21242,7 @@
       <c r="A694" t="s">
         <v>1269</v>
       </c>
-      <c r="B694" s="4" t="s">
+      <c r="B694" s="3" t="s">
         <v>1402</v>
       </c>
       <c r="C694">
@@ -21275,7 +21262,7 @@
       <c r="A695" t="s">
         <v>1269</v>
       </c>
-      <c r="B695" s="4" t="s">
+      <c r="B695" s="3" t="s">
         <v>1404</v>
       </c>
       <c r="C695">
@@ -21295,7 +21282,7 @@
       <c r="A696" t="s">
         <v>1269</v>
       </c>
-      <c r="B696" s="4" t="s">
+      <c r="B696" s="3" t="s">
         <v>1406</v>
       </c>
       <c r="C696">
@@ -21315,7 +21302,7 @@
       <c r="A697" t="s">
         <v>1269</v>
       </c>
-      <c r="B697" s="4" t="s">
+      <c r="B697" s="3" t="s">
         <v>1408</v>
       </c>
       <c r="C697">
@@ -21335,7 +21322,7 @@
       <c r="A698" t="s">
         <v>1269</v>
       </c>
-      <c r="B698" s="4" t="s">
+      <c r="B698" s="3" t="s">
         <v>1410</v>
       </c>
       <c r="C698">
@@ -21355,7 +21342,7 @@
       <c r="A699" t="s">
         <v>1269</v>
       </c>
-      <c r="B699" s="4" t="s">
+      <c r="B699" s="3" t="s">
         <v>1412</v>
       </c>
       <c r="C699">
@@ -21375,7 +21362,7 @@
       <c r="A700" t="s">
         <v>1269</v>
       </c>
-      <c r="B700" s="4" t="s">
+      <c r="B700" s="3" t="s">
         <v>1414</v>
       </c>
       <c r="C700">
@@ -21398,7 +21385,7 @@
       <c r="A701" t="s">
         <v>1269</v>
       </c>
-      <c r="B701" s="4" t="s">
+      <c r="B701" s="3" t="s">
         <v>1416</v>
       </c>
       <c r="C701">
@@ -21421,7 +21408,7 @@
       <c r="A702" t="s">
         <v>1269</v>
       </c>
-      <c r="B702" s="4" t="s">
+      <c r="B702" s="3" t="s">
         <v>1418</v>
       </c>
       <c r="C702">
@@ -21444,7 +21431,7 @@
       <c r="A703" t="s">
         <v>1269</v>
       </c>
-      <c r="B703" s="4" t="s">
+      <c r="B703" s="3" t="s">
         <v>1420</v>
       </c>
       <c r="C703">
@@ -21464,7 +21451,7 @@
       <c r="A704" t="s">
         <v>1269</v>
       </c>
-      <c r="B704" s="4" t="s">
+      <c r="B704" s="3" t="s">
         <v>1422</v>
       </c>
       <c r="C704">
@@ -21484,7 +21471,7 @@
       <c r="A705" t="s">
         <v>1269</v>
       </c>
-      <c r="B705" s="4" t="s">
+      <c r="B705" s="3" t="s">
         <v>1424</v>
       </c>
       <c r="C705">
@@ -21504,7 +21491,7 @@
       <c r="A706" t="s">
         <v>1269</v>
       </c>
-      <c r="B706" s="4" t="s">
+      <c r="B706" s="3" t="s">
         <v>1426</v>
       </c>
       <c r="C706">
@@ -21524,7 +21511,7 @@
       <c r="A707" t="s">
         <v>1269</v>
       </c>
-      <c r="B707" s="4" t="s">
+      <c r="B707" s="3" t="s">
         <v>1428</v>
       </c>
       <c r="C707">
@@ -21544,7 +21531,7 @@
       <c r="A708" t="s">
         <v>1269</v>
       </c>
-      <c r="B708" s="4" t="s">
+      <c r="B708" s="3" t="s">
         <v>1430</v>
       </c>
       <c r="C708">
@@ -21564,7 +21551,7 @@
       <c r="A709" t="s">
         <v>1269</v>
       </c>
-      <c r="B709" s="4" t="s">
+      <c r="B709" s="3" t="s">
         <v>1432</v>
       </c>
       <c r="C709">
@@ -21584,7 +21571,7 @@
       <c r="A710" t="s">
         <v>1269</v>
       </c>
-      <c r="B710" s="4" t="s">
+      <c r="B710" s="3" t="s">
         <v>1434</v>
       </c>
       <c r="C710">
@@ -21604,7 +21591,7 @@
       <c r="A711" t="s">
         <v>1269</v>
       </c>
-      <c r="B711" s="4" t="s">
+      <c r="B711" s="3" t="s">
         <v>1436</v>
       </c>
       <c r="C711">
@@ -21624,7 +21611,7 @@
       <c r="A712" t="s">
         <v>1269</v>
       </c>
-      <c r="B712" s="4" t="s">
+      <c r="B712" s="3" t="s">
         <v>1438</v>
       </c>
       <c r="C712">
@@ -21644,7 +21631,7 @@
       <c r="A713" t="s">
         <v>1269</v>
       </c>
-      <c r="B713" s="4" t="s">
+      <c r="B713" s="3" t="s">
         <v>1440</v>
       </c>
       <c r="C713">
@@ -21664,7 +21651,7 @@
       <c r="A714" t="s">
         <v>1269</v>
       </c>
-      <c r="B714" s="4" t="s">
+      <c r="B714" s="3" t="s">
         <v>1442</v>
       </c>
       <c r="C714">
@@ -21684,7 +21671,7 @@
       <c r="A715" t="s">
         <v>1269</v>
       </c>
-      <c r="B715" s="4" t="s">
+      <c r="B715" s="3" t="s">
         <v>1444</v>
       </c>
       <c r="C715">
@@ -21704,7 +21691,7 @@
       <c r="A716" t="s">
         <v>1269</v>
       </c>
-      <c r="B716" s="4" t="s">
+      <c r="B716" s="3" t="s">
         <v>1446</v>
       </c>
       <c r="C716">
@@ -21724,7 +21711,7 @@
       <c r="A717" t="s">
         <v>1269</v>
       </c>
-      <c r="B717" s="4" t="s">
+      <c r="B717" s="3" t="s">
         <v>1448</v>
       </c>
       <c r="C717">
@@ -21744,7 +21731,7 @@
       <c r="A718" t="s">
         <v>1269</v>
       </c>
-      <c r="B718" s="4" t="s">
+      <c r="B718" s="3" t="s">
         <v>1450</v>
       </c>
       <c r="C718">
@@ -21764,7 +21751,7 @@
       <c r="A719" t="s">
         <v>1269</v>
       </c>
-      <c r="B719" s="4" t="s">
+      <c r="B719" s="3" t="s">
         <v>1452</v>
       </c>
       <c r="C719">
@@ -21784,7 +21771,7 @@
       <c r="A720" t="s">
         <v>1269</v>
       </c>
-      <c r="B720" s="4" t="s">
+      <c r="B720" s="3" t="s">
         <v>1454</v>
       </c>
       <c r="C720">
@@ -21807,7 +21794,7 @@
       <c r="A721" t="s">
         <v>1269</v>
       </c>
-      <c r="B721" s="4" t="s">
+      <c r="B721" s="3" t="s">
         <v>1456</v>
       </c>
       <c r="C721">
@@ -21827,7 +21814,7 @@
       <c r="A722" t="s">
         <v>1269</v>
       </c>
-      <c r="B722" s="4" t="s">
+      <c r="B722" s="3" t="s">
         <v>1458</v>
       </c>
       <c r="C722">
@@ -21847,7 +21834,7 @@
       <c r="A723" t="s">
         <v>1269</v>
       </c>
-      <c r="B723" s="4" t="s">
+      <c r="B723" s="3" t="s">
         <v>1460</v>
       </c>
       <c r="C723">
@@ -21870,7 +21857,7 @@
       <c r="A724" t="s">
         <v>1269</v>
       </c>
-      <c r="B724" s="4" t="s">
+      <c r="B724" s="3" t="s">
         <v>1462</v>
       </c>
       <c r="C724">
@@ -21890,7 +21877,7 @@
       <c r="A725" t="s">
         <v>1269</v>
       </c>
-      <c r="B725" s="4" t="s">
+      <c r="B725" s="3" t="s">
         <v>1464</v>
       </c>
       <c r="C725">
@@ -21910,7 +21897,7 @@
       <c r="A726" t="s">
         <v>1269</v>
       </c>
-      <c r="B726" s="4" t="s">
+      <c r="B726" s="3" t="s">
         <v>1466</v>
       </c>
       <c r="C726">
@@ -21930,7 +21917,7 @@
       <c r="A727" t="s">
         <v>1269</v>
       </c>
-      <c r="B727" s="4" t="s">
+      <c r="B727" s="3" t="s">
         <v>1468</v>
       </c>
       <c r="C727">
@@ -21953,7 +21940,7 @@
       <c r="A728" t="s">
         <v>1269</v>
       </c>
-      <c r="B728" s="4" t="s">
+      <c r="B728" s="3" t="s">
         <v>1470</v>
       </c>
       <c r="C728">
@@ -21976,7 +21963,7 @@
       <c r="A729" t="s">
         <v>1269</v>
       </c>
-      <c r="B729" s="4" t="s">
+      <c r="B729" s="3" t="s">
         <v>1472</v>
       </c>
       <c r="C729">
@@ -21999,7 +21986,7 @@
       <c r="A730" t="s">
         <v>1269</v>
       </c>
-      <c r="B730" s="4" t="s">
+      <c r="B730" s="3" t="s">
         <v>1474</v>
       </c>
       <c r="C730">
@@ -22022,7 +22009,7 @@
       <c r="A731" t="s">
         <v>1269</v>
       </c>
-      <c r="B731" s="4" t="s">
+      <c r="B731" s="3" t="s">
         <v>1476</v>
       </c>
       <c r="C731">
@@ -22045,7 +22032,7 @@
       <c r="A732" t="s">
         <v>1269</v>
       </c>
-      <c r="B732" s="4" t="s">
+      <c r="B732" s="3" t="s">
         <v>1478</v>
       </c>
       <c r="C732">
@@ -22068,7 +22055,7 @@
       <c r="A733" t="s">
         <v>1269</v>
       </c>
-      <c r="B733" s="4" t="s">
+      <c r="B733" s="3" t="s">
         <v>1480</v>
       </c>
       <c r="C733">
@@ -22091,7 +22078,7 @@
       <c r="A734" t="s">
         <v>1269</v>
       </c>
-      <c r="B734" s="4" t="s">
+      <c r="B734" s="3" t="s">
         <v>1482</v>
       </c>
       <c r="C734">
@@ -22114,7 +22101,7 @@
       <c r="A735" t="s">
         <v>1269</v>
       </c>
-      <c r="B735" s="4" t="s">
+      <c r="B735" s="3" t="s">
         <v>1484</v>
       </c>
       <c r="C735">
@@ -22137,7 +22124,7 @@
       <c r="A736" t="s">
         <v>1269</v>
       </c>
-      <c r="B736" s="4" t="s">
+      <c r="B736" s="3" t="s">
         <v>1486</v>
       </c>
       <c r="C736">
@@ -22160,7 +22147,7 @@
       <c r="A737" t="s">
         <v>1269</v>
       </c>
-      <c r="B737" s="4" t="s">
+      <c r="B737" s="3" t="s">
         <v>1488</v>
       </c>
       <c r="C737">
@@ -22183,7 +22170,7 @@
       <c r="A738" t="s">
         <v>1269</v>
       </c>
-      <c r="B738" s="4" t="s">
+      <c r="B738" s="3" t="s">
         <v>1490</v>
       </c>
       <c r="C738">
@@ -22206,7 +22193,7 @@
       <c r="A739" t="s">
         <v>1269</v>
       </c>
-      <c r="B739" s="4" t="s">
+      <c r="B739" s="3" t="s">
         <v>1492</v>
       </c>
       <c r="C739">
@@ -22229,7 +22216,7 @@
       <c r="A740" t="s">
         <v>1269</v>
       </c>
-      <c r="B740" s="4" t="s">
+      <c r="B740" s="3" t="s">
         <v>1494</v>
       </c>
       <c r="C740">
@@ -22252,7 +22239,7 @@
       <c r="A741" t="s">
         <v>1269</v>
       </c>
-      <c r="B741" s="4" t="s">
+      <c r="B741" s="3" t="s">
         <v>1496</v>
       </c>
       <c r="C741">
@@ -22275,7 +22262,7 @@
       <c r="A742" t="s">
         <v>1269</v>
       </c>
-      <c r="B742" s="4" t="s">
+      <c r="B742" s="3" t="s">
         <v>1498</v>
       </c>
       <c r="C742">
@@ -22298,7 +22285,7 @@
       <c r="A743" t="s">
         <v>1269</v>
       </c>
-      <c r="B743" s="4" t="s">
+      <c r="B743" s="3" t="s">
         <v>1500</v>
       </c>
       <c r="C743">
@@ -22321,7 +22308,7 @@
       <c r="A744" t="s">
         <v>1269</v>
       </c>
-      <c r="B744" s="4" t="s">
+      <c r="B744" s="3" t="s">
         <v>1502</v>
       </c>
       <c r="C744">
@@ -22344,7 +22331,7 @@
       <c r="A745" t="s">
         <v>1269</v>
       </c>
-      <c r="B745" s="4" t="s">
+      <c r="B745" s="3" t="s">
         <v>1504</v>
       </c>
       <c r="C745">
@@ -22367,7 +22354,7 @@
       <c r="A746" t="s">
         <v>1269</v>
       </c>
-      <c r="B746" s="4" t="s">
+      <c r="B746" s="3" t="s">
         <v>1506</v>
       </c>
       <c r="C746">
@@ -22390,7 +22377,7 @@
       <c r="A747" t="s">
         <v>1269</v>
       </c>
-      <c r="B747" s="4" t="s">
+      <c r="B747" s="3" t="s">
         <v>1508</v>
       </c>
       <c r="C747">
@@ -22413,7 +22400,7 @@
       <c r="A748" t="s">
         <v>1269</v>
       </c>
-      <c r="B748" s="4" t="s">
+      <c r="B748" s="3" t="s">
         <v>1510</v>
       </c>
       <c r="C748">
@@ -22436,7 +22423,7 @@
       <c r="A749" t="s">
         <v>1269</v>
       </c>
-      <c r="B749" s="4" t="s">
+      <c r="B749" s="3" t="s">
         <v>1512</v>
       </c>
       <c r="C749">
@@ -22459,7 +22446,7 @@
       <c r="A750" t="s">
         <v>1269</v>
       </c>
-      <c r="B750" s="4" t="s">
+      <c r="B750" s="3" t="s">
         <v>1514</v>
       </c>
       <c r="C750">
@@ -22482,7 +22469,7 @@
       <c r="A751" t="s">
         <v>1269</v>
       </c>
-      <c r="B751" s="4" t="s">
+      <c r="B751" s="3" t="s">
         <v>1516</v>
       </c>
       <c r="C751">
@@ -22505,7 +22492,7 @@
       <c r="A752" t="s">
         <v>1269</v>
       </c>
-      <c r="B752" s="4" t="s">
+      <c r="B752" s="3" t="s">
         <v>1518</v>
       </c>
       <c r="C752">
@@ -22528,7 +22515,7 @@
       <c r="A753" t="s">
         <v>1269</v>
       </c>
-      <c r="B753" s="4" t="s">
+      <c r="B753" s="3" t="s">
         <v>1520</v>
       </c>
       <c r="C753">
@@ -22551,7 +22538,7 @@
       <c r="A754" t="s">
         <v>1269</v>
       </c>
-      <c r="B754" s="4" t="s">
+      <c r="B754" s="3" t="s">
         <v>1522</v>
       </c>
       <c r="C754">
@@ -22574,7 +22561,7 @@
       <c r="A755" t="s">
         <v>1269</v>
       </c>
-      <c r="B755" s="4" t="s">
+      <c r="B755" s="3" t="s">
         <v>1524</v>
       </c>
       <c r="C755">
@@ -22597,7 +22584,7 @@
       <c r="A756" t="s">
         <v>1269</v>
       </c>
-      <c r="B756" s="4" t="s">
+      <c r="B756" s="3" t="s">
         <v>1526</v>
       </c>
       <c r="C756">
@@ -22620,7 +22607,7 @@
       <c r="A757" t="s">
         <v>1269</v>
       </c>
-      <c r="B757" s="4" t="s">
+      <c r="B757" s="3" t="s">
         <v>1528</v>
       </c>
       <c r="C757">
@@ -22643,7 +22630,7 @@
       <c r="A758" t="s">
         <v>1269</v>
       </c>
-      <c r="B758" s="4" t="s">
+      <c r="B758" s="3" t="s">
         <v>1530</v>
       </c>
       <c r="C758">
@@ -22666,7 +22653,7 @@
       <c r="A759" t="s">
         <v>1269</v>
       </c>
-      <c r="B759" s="4" t="s">
+      <c r="B759" s="3" t="s">
         <v>1532</v>
       </c>
       <c r="C759">
@@ -22689,7 +22676,7 @@
       <c r="A760" t="s">
         <v>1269</v>
       </c>
-      <c r="B760" s="4" t="s">
+      <c r="B760" s="3" t="s">
         <v>1534</v>
       </c>
       <c r="C760">
@@ -22712,7 +22699,7 @@
       <c r="A761" t="s">
         <v>1269</v>
       </c>
-      <c r="B761" s="4" t="s">
+      <c r="B761" s="3" t="s">
         <v>1536</v>
       </c>
       <c r="C761">
@@ -22735,7 +22722,7 @@
       <c r="A762" t="s">
         <v>1269</v>
       </c>
-      <c r="B762" s="4" t="s">
+      <c r="B762" s="3" t="s">
         <v>1538</v>
       </c>
       <c r="C762">
@@ -22758,7 +22745,7 @@
       <c r="A763" t="s">
         <v>1269</v>
       </c>
-      <c r="B763" s="4" t="s">
+      <c r="B763" s="3" t="s">
         <v>1540</v>
       </c>
       <c r="C763">
@@ -22781,7 +22768,7 @@
       <c r="A764" t="s">
         <v>1269</v>
       </c>
-      <c r="B764" s="4" t="s">
+      <c r="B764" s="3" t="s">
         <v>1542</v>
       </c>
       <c r="C764">
@@ -22804,7 +22791,7 @@
       <c r="A765" t="s">
         <v>1269</v>
       </c>
-      <c r="B765" s="4" t="s">
+      <c r="B765" s="3" t="s">
         <v>1544</v>
       </c>
       <c r="C765">
@@ -22827,7 +22814,7 @@
       <c r="A766" t="s">
         <v>1269</v>
       </c>
-      <c r="B766" s="4" t="s">
+      <c r="B766" s="3" t="s">
         <v>1546</v>
       </c>
       <c r="C766">
@@ -22850,7 +22837,7 @@
       <c r="A767" t="s">
         <v>1269</v>
       </c>
-      <c r="B767" s="4" t="s">
+      <c r="B767" s="3" t="s">
         <v>1548</v>
       </c>
       <c r="C767">
@@ -22873,7 +22860,7 @@
       <c r="A768" t="s">
         <v>1269</v>
       </c>
-      <c r="B768" s="4" t="s">
+      <c r="B768" s="3" t="s">
         <v>1550</v>
       </c>
       <c r="C768">
@@ -22893,7 +22880,7 @@
       <c r="A769" t="s">
         <v>1269</v>
       </c>
-      <c r="B769" s="4" t="s">
+      <c r="B769" s="3" t="s">
         <v>1552</v>
       </c>
       <c r="C769">
@@ -22913,7 +22900,7 @@
       <c r="A770" t="s">
         <v>1269</v>
       </c>
-      <c r="B770" s="4" t="s">
+      <c r="B770" s="3" t="s">
         <v>1554</v>
       </c>
       <c r="C770">
@@ -22936,7 +22923,7 @@
       <c r="A771" t="s">
         <v>1269</v>
       </c>
-      <c r="B771" s="4" t="s">
+      <c r="B771" s="3" t="s">
         <v>1556</v>
       </c>
       <c r="C771">
@@ -22956,7 +22943,7 @@
       <c r="A772" t="s">
         <v>1269</v>
       </c>
-      <c r="B772" s="4" t="s">
+      <c r="B772" s="3" t="s">
         <v>1558</v>
       </c>
       <c r="C772">
@@ -22976,7 +22963,7 @@
       <c r="A773" t="s">
         <v>1269</v>
       </c>
-      <c r="B773" s="4" t="s">
+      <c r="B773" s="3" t="s">
         <v>1560</v>
       </c>
       <c r="C773">
@@ -22996,7 +22983,7 @@
       <c r="A774" t="s">
         <v>1269</v>
       </c>
-      <c r="B774" s="4" t="s">
+      <c r="B774" s="3" t="s">
         <v>1562</v>
       </c>
       <c r="C774">
@@ -23016,7 +23003,7 @@
       <c r="A775" t="s">
         <v>1269</v>
       </c>
-      <c r="B775" s="4" t="s">
+      <c r="B775" s="3" t="s">
         <v>1564</v>
       </c>
       <c r="C775">
@@ -23036,7 +23023,7 @@
       <c r="A776" t="s">
         <v>1269</v>
       </c>
-      <c r="B776" s="4" t="s">
+      <c r="B776" s="3" t="s">
         <v>1566</v>
       </c>
       <c r="C776">
@@ -23056,7 +23043,7 @@
       <c r="A777" t="s">
         <v>1269</v>
       </c>
-      <c r="B777" s="4" t="s">
+      <c r="B777" s="3" t="s">
         <v>1568</v>
       </c>
       <c r="C777">
@@ -23076,7 +23063,7 @@
       <c r="A778" t="s">
         <v>1269</v>
       </c>
-      <c r="B778" s="4" t="s">
+      <c r="B778" s="3" t="s">
         <v>1570</v>
       </c>
       <c r="C778">
@@ -23096,7 +23083,7 @@
       <c r="A779" t="s">
         <v>1269</v>
       </c>
-      <c r="B779" s="4" t="s">
+      <c r="B779" s="3" t="s">
         <v>1572</v>
       </c>
       <c r="C779">
@@ -23116,7 +23103,7 @@
       <c r="A780" t="s">
         <v>1269</v>
       </c>
-      <c r="B780" s="4" t="s">
+      <c r="B780" s="3" t="s">
         <v>1574</v>
       </c>
       <c r="C780">
@@ -23139,7 +23126,7 @@
       <c r="A781" t="s">
         <v>1269</v>
       </c>
-      <c r="B781" s="4" t="s">
+      <c r="B781" s="3" t="s">
         <v>1576</v>
       </c>
       <c r="C781">
@@ -23162,7 +23149,7 @@
       <c r="A782" t="s">
         <v>1269</v>
       </c>
-      <c r="B782" s="4" t="s">
+      <c r="B782" s="3" t="s">
         <v>1578</v>
       </c>
       <c r="C782">
@@ -23185,7 +23172,7 @@
       <c r="A783" t="s">
         <v>1269</v>
       </c>
-      <c r="B783" s="4" t="s">
+      <c r="B783" s="3" t="s">
         <v>1580</v>
       </c>
       <c r="C783">
@@ -23208,7 +23195,7 @@
       <c r="A784" t="s">
         <v>1269</v>
       </c>
-      <c r="B784" s="4" t="s">
+      <c r="B784" s="3" t="s">
         <v>1582</v>
       </c>
       <c r="C784">
@@ -23231,7 +23218,7 @@
       <c r="A785" t="s">
         <v>1269</v>
       </c>
-      <c r="B785" s="4" t="s">
+      <c r="B785" s="3" t="s">
         <v>1584</v>
       </c>
       <c r="C785">
@@ -23251,7 +23238,7 @@
       <c r="A786" t="s">
         <v>1269</v>
       </c>
-      <c r="B786" s="4" t="s">
+      <c r="B786" s="3" t="s">
         <v>1586</v>
       </c>
       <c r="C786">
@@ -23271,7 +23258,7 @@
       <c r="A787" t="s">
         <v>1269</v>
       </c>
-      <c r="B787" s="4" t="s">
+      <c r="B787" s="3" t="s">
         <v>1588</v>
       </c>
       <c r="C787">
@@ -23294,7 +23281,7 @@
       <c r="A788" t="s">
         <v>1269</v>
       </c>
-      <c r="B788" s="4" t="s">
+      <c r="B788" s="3" t="s">
         <v>1590</v>
       </c>
       <c r="C788">
@@ -23314,7 +23301,7 @@
       <c r="A789" t="s">
         <v>1269</v>
       </c>
-      <c r="B789" s="4" t="s">
+      <c r="B789" s="3" t="s">
         <v>1592</v>
       </c>
       <c r="C789">
@@ -23334,7 +23321,7 @@
       <c r="A790" t="s">
         <v>1269</v>
       </c>
-      <c r="B790" s="4" t="s">
+      <c r="B790" s="3" t="s">
         <v>1594</v>
       </c>
       <c r="C790">
@@ -23357,7 +23344,7 @@
       <c r="A791" t="s">
         <v>1269</v>
       </c>
-      <c r="B791" s="4" t="s">
+      <c r="B791" s="3" t="s">
         <v>1596</v>
       </c>
       <c r="C791">
@@ -23380,7 +23367,7 @@
       <c r="A792" t="s">
         <v>1269</v>
       </c>
-      <c r="B792" s="4" t="s">
+      <c r="B792" s="3" t="s">
         <v>1598</v>
       </c>
       <c r="C792">
@@ -23403,7 +23390,7 @@
       <c r="A793" t="s">
         <v>1269</v>
       </c>
-      <c r="B793" s="4" t="s">
+      <c r="B793" s="3" t="s">
         <v>1600</v>
       </c>
       <c r="C793">
@@ -23426,7 +23413,7 @@
       <c r="A794" t="s">
         <v>1269</v>
       </c>
-      <c r="B794" s="4" t="s">
+      <c r="B794" s="3" t="s">
         <v>1602</v>
       </c>
       <c r="C794">
@@ -23446,7 +23433,7 @@
       <c r="A795" t="s">
         <v>1269</v>
       </c>
-      <c r="B795" s="4" t="s">
+      <c r="B795" s="3" t="s">
         <v>1604</v>
       </c>
       <c r="C795">
@@ -23469,7 +23456,7 @@
       <c r="A796" t="s">
         <v>1269</v>
       </c>
-      <c r="B796" s="4" t="s">
+      <c r="B796" s="3" t="s">
         <v>1606</v>
       </c>
       <c r="C796">
@@ -23489,7 +23476,7 @@
       <c r="A797" t="s">
         <v>1269</v>
       </c>
-      <c r="B797" s="4" t="s">
+      <c r="B797" s="3" t="s">
         <v>1608</v>
       </c>
       <c r="C797">
@@ -23512,7 +23499,7 @@
       <c r="A798" t="s">
         <v>1269</v>
       </c>
-      <c r="B798" s="4" t="s">
+      <c r="B798" s="3" t="s">
         <v>1610</v>
       </c>
       <c r="C798">
@@ -23532,7 +23519,7 @@
       <c r="A799" t="s">
         <v>1269</v>
       </c>
-      <c r="B799" s="4" t="s">
+      <c r="B799" s="3" t="s">
         <v>1612</v>
       </c>
       <c r="C799">
@@ -23552,7 +23539,7 @@
       <c r="A800" t="s">
         <v>1269</v>
       </c>
-      <c r="B800" s="4" t="s">
+      <c r="B800" s="3" t="s">
         <v>1614</v>
       </c>
       <c r="C800">
@@ -23572,7 +23559,7 @@
       <c r="A801" t="s">
         <v>1269</v>
       </c>
-      <c r="B801" s="4" t="s">
+      <c r="B801" s="3" t="s">
         <v>1616</v>
       </c>
       <c r="C801">
@@ -23592,7 +23579,7 @@
       <c r="A802" t="s">
         <v>1269</v>
       </c>
-      <c r="B802" s="4" t="s">
+      <c r="B802" s="3" t="s">
         <v>1618</v>
       </c>
       <c r="C802">
@@ -23612,7 +23599,7 @@
       <c r="A803" t="s">
         <v>1269</v>
       </c>
-      <c r="B803" s="4" t="s">
+      <c r="B803" s="3" t="s">
         <v>1620</v>
       </c>
       <c r="C803">
@@ -23632,7 +23619,7 @@
       <c r="A804" t="s">
         <v>1269</v>
       </c>
-      <c r="B804" s="4" t="s">
+      <c r="B804" s="3" t="s">
         <v>1622</v>
       </c>
       <c r="C804">
@@ -23652,7 +23639,7 @@
       <c r="A805" t="s">
         <v>1269</v>
       </c>
-      <c r="B805" s="4" t="s">
+      <c r="B805" s="3" t="s">
         <v>1624</v>
       </c>
       <c r="C805">
@@ -23672,7 +23659,7 @@
       <c r="A806" t="s">
         <v>1269</v>
       </c>
-      <c r="B806" s="4" t="s">
+      <c r="B806" s="3" t="s">
         <v>1626</v>
       </c>
       <c r="C806">
@@ -23692,7 +23679,7 @@
       <c r="A807" t="s">
         <v>1269</v>
       </c>
-      <c r="B807" s="4" t="s">
+      <c r="B807" s="3" t="s">
         <v>1628</v>
       </c>
       <c r="C807">
@@ -23712,7 +23699,7 @@
       <c r="A808" t="s">
         <v>1269</v>
       </c>
-      <c r="B808" s="4" t="s">
+      <c r="B808" s="3" t="s">
         <v>1630</v>
       </c>
       <c r="C808">
@@ -23732,7 +23719,7 @@
       <c r="A809" t="s">
         <v>1269</v>
       </c>
-      <c r="B809" s="4" t="s">
+      <c r="B809" s="3" t="s">
         <v>1632</v>
       </c>
       <c r="C809">
@@ -23752,7 +23739,7 @@
       <c r="A810" t="s">
         <v>1269</v>
       </c>
-      <c r="B810" s="4" t="s">
+      <c r="B810" s="3" t="s">
         <v>1633</v>
       </c>
       <c r="C810">
@@ -23772,7 +23759,7 @@
       <c r="A811" t="s">
         <v>1269</v>
       </c>
-      <c r="B811" s="4" t="s">
+      <c r="B811" s="3" t="s">
         <v>1635</v>
       </c>
       <c r="C811">
@@ -23792,7 +23779,7 @@
       <c r="A812" t="s">
         <v>1269</v>
       </c>
-      <c r="B812" s="4" t="s">
+      <c r="B812" s="3" t="s">
         <v>1637</v>
       </c>
       <c r="C812">
@@ -23812,7 +23799,7 @@
       <c r="A813" t="s">
         <v>1269</v>
       </c>
-      <c r="B813" s="4" t="s">
+      <c r="B813" s="3" t="s">
         <v>1639</v>
       </c>
       <c r="C813">
@@ -23832,7 +23819,7 @@
       <c r="A814" t="s">
         <v>1269</v>
       </c>
-      <c r="B814" s="4" t="s">
+      <c r="B814" s="3" t="s">
         <v>1641</v>
       </c>
       <c r="C814">
@@ -23855,7 +23842,7 @@
       <c r="A815" t="s">
         <v>1269</v>
       </c>
-      <c r="B815" s="4" t="s">
+      <c r="B815" s="3" t="s">
         <v>1643</v>
       </c>
       <c r="C815">
@@ -23875,7 +23862,7 @@
       <c r="A816" t="s">
         <v>1269</v>
       </c>
-      <c r="B816" s="4" t="s">
+      <c r="B816" s="3" t="s">
         <v>1645</v>
       </c>
       <c r="C816">
@@ -23895,7 +23882,7 @@
       <c r="A817" t="s">
         <v>1269</v>
       </c>
-      <c r="B817" s="4" t="s">
+      <c r="B817" s="3" t="s">
         <v>1647</v>
       </c>
       <c r="C817">
@@ -23915,7 +23902,7 @@
       <c r="A818" t="s">
         <v>1269</v>
       </c>
-      <c r="B818" s="4" t="s">
+      <c r="B818" s="3" t="s">
         <v>1649</v>
       </c>
       <c r="C818">
@@ -23938,7 +23925,7 @@
       <c r="A819" t="s">
         <v>1269</v>
       </c>
-      <c r="B819" s="4" t="s">
+      <c r="B819" s="3" t="s">
         <v>1651</v>
       </c>
       <c r="C819">
@@ -23958,7 +23945,7 @@
       <c r="A820" t="s">
         <v>1269</v>
       </c>
-      <c r="B820" s="4" t="s">
+      <c r="B820" s="3" t="s">
         <v>1653</v>
       </c>
       <c r="C820">
@@ -23981,7 +23968,7 @@
       <c r="A821" t="s">
         <v>1269</v>
       </c>
-      <c r="B821" s="4" t="s">
+      <c r="B821" s="3" t="s">
         <v>1655</v>
       </c>
       <c r="C821">
@@ -24001,7 +23988,7 @@
       <c r="A822" t="s">
         <v>1269</v>
       </c>
-      <c r="B822" s="4" t="s">
+      <c r="B822" s="3" t="s">
         <v>1657</v>
       </c>
       <c r="C822">
@@ -24021,7 +24008,7 @@
       <c r="A823" t="s">
         <v>1269</v>
       </c>
-      <c r="B823" s="4" t="s">
+      <c r="B823" s="3" t="s">
         <v>1659</v>
       </c>
       <c r="C823">
@@ -24041,7 +24028,7 @@
       <c r="A824" t="s">
         <v>1269</v>
       </c>
-      <c r="B824" s="4" t="s">
+      <c r="B824" s="3" t="s">
         <v>1661</v>
       </c>
       <c r="C824">
@@ -24061,7 +24048,7 @@
       <c r="A825" t="s">
         <v>1269</v>
       </c>
-      <c r="B825" s="4" t="s">
+      <c r="B825" s="3" t="s">
         <v>1663</v>
       </c>
       <c r="C825">
@@ -24081,7 +24068,7 @@
       <c r="A826" t="s">
         <v>1269</v>
       </c>
-      <c r="B826" s="4" t="s">
+      <c r="B826" s="3" t="s">
         <v>1665</v>
       </c>
       <c r="C826">
@@ -24101,7 +24088,7 @@
       <c r="A827" t="s">
         <v>1269</v>
       </c>
-      <c r="B827" s="4" t="s">
+      <c r="B827" s="3" t="s">
         <v>1667</v>
       </c>
       <c r="C827">
@@ -24121,7 +24108,7 @@
       <c r="A828" t="s">
         <v>1269</v>
       </c>
-      <c r="B828" s="4" t="s">
+      <c r="B828" s="3" t="s">
         <v>1669</v>
       </c>
       <c r="C828">
@@ -24141,7 +24128,7 @@
       <c r="A829" t="s">
         <v>1269</v>
       </c>
-      <c r="B829" s="4" t="s">
+      <c r="B829" s="3" t="s">
         <v>1671</v>
       </c>
       <c r="C829">
@@ -26593,18 +26580,7 @@
     <protectedRange sqref="E88:G95" name="区域1_1_1"/>
   </protectedRanges>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G943" etc:filterBottomFollowUsedRange="0">
-    <extLst>
-      <etc:autoFilterAnalysis etc:version="v1" etc:showPane="0">
-        <etc:analysisCharts>
-          <etc:chart etc:type="pie">
-            <etc:category etc:colId="5"/>
-            <etc:seriesCollections etc:count="1">
-              <etc:series etc:colId="5" etc:subtotal="count"/>
-            </etc:seriesCollections>
-          </etc:chart>
-        </etc:analysisCharts>
-      </etc:autoFilterAnalysis>
-    </extLst>
+    <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
